--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/paddle_variants_abbyy_artifacts.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/paddle_variants_abbyy_artifacts.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overall Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Overall Summary" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Overall Summary'!$A$1:$AA$241</definedName>
@@ -444,7 +444,7 @@
     <col width="22" customWidth="1" min="21" max="21"/>
     <col width="27" customWidth="1" min="22" max="22"/>
     <col width="27" customWidth="1" min="23" max="23"/>
-    <col width="71" customWidth="1" min="24" max="24"/>
+    <col width="90" customWidth="1" min="24" max="24"/>
     <col width="24" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -676,7 +676,7 @@
         <v>10614</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>7874</v>
+        <v>7847</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>11041</v>
@@ -799,7 +799,7 @@
         <v>110</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E9" s="1" t="inlineStr"/>
       <c r="F9" s="1" t="n"/>
@@ -877,10 +877,10 @@
         <v>60</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F11" s="1" t="n"/>
       <c r="G11" s="1" t="n"/>
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="M15" s="1" t="n">
-        <v>2668</v>
+        <v>2665</v>
       </c>
       <c r="N15" s="1" t="n">
         <v>5886</v>
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="M16" s="1" t="n">
-        <v>2573</v>
+        <v>2559</v>
       </c>
       <c r="N16" s="1" t="n">
         <v>20186</v>
@@ -1290,7 +1290,7 @@
         </is>
       </c>
       <c r="M17" s="1" t="n">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="N17" s="1" t="n">
         <v>5493</v>
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="M18" s="1" t="n">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="N18" s="1" t="n">
         <v>7274</v>
@@ -1456,7 +1456,7 @@
         </is>
       </c>
       <c r="M19" s="1" t="n">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="N19" s="1" t="n">
         <v>3943</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="Q25" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\aeu.00037_19470820\aeu.00037_19470820.1.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\aeu.00037_19470820\aeu.00037_19470820.1.txt</t>
         </is>
       </c>
       <c r="R25" s="1" t="n">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="X25" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\aeu.00037_19470820\aeu.00037_19470820.1.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\aeu.00037_19470820\aeu.00037_19470820.1.txt</t>
         </is>
       </c>
       <c r="Y25" s="1" t="n">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="Q26" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\aeu.00037_19470820\aeu.00037_19470820.2.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\aeu.00037_19470820\aeu.00037_19470820.2.txt</t>
         </is>
       </c>
       <c r="R26" s="1" t="n">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="X26" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\aeu.00037_19470820\aeu.00037_19470820.2.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\aeu.00037_19470820\aeu.00037_19470820.2.txt</t>
         </is>
       </c>
       <c r="Y26" s="1" t="n">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="Q27" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\aeu.00037_19470820\aeu.00037_19470820.3.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\aeu.00037_19470820\aeu.00037_19470820.3.txt</t>
         </is>
       </c>
       <c r="R27" s="1" t="n">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="X27" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\aeu.00037_19470820\aeu.00037_19470820.3.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\aeu.00037_19470820\aeu.00037_19470820.3.txt</t>
         </is>
       </c>
       <c r="Y27" s="1" t="n">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="Q28" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\aeu.00037_19470820\aeu.00037_19470820.4.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\aeu.00037_19470820\aeu.00037_19470820.4.txt</t>
         </is>
       </c>
       <c r="R28" s="1" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="X28" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\aeu.00037_19470820\aeu.00037_19470820.4.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\aeu.00037_19470820\aeu.00037_19470820.4.txt</t>
         </is>
       </c>
       <c r="Y28" s="1" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="Q29" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\aeu.00037_19470820\aeu.00037_19470820.5.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\aeu.00037_19470820\aeu.00037_19470820.5.txt</t>
         </is>
       </c>
       <c r="R29" s="1" t="n">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="X29" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\aeu.00037_19470820\aeu.00037_19470820.5.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\aeu.00037_19470820\aeu.00037_19470820.5.txt</t>
         </is>
       </c>
       <c r="Y29" s="1" t="n">
@@ -2458,14 +2458,14 @@
       </c>
       <c r="Q30" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\aeu.00037_19470820\aeu.00037_19470820.6.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\aeu.00037_19470820\aeu.00037_19470820.6.txt</t>
         </is>
       </c>
       <c r="R30" s="1" t="n">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="S30" s="1" t="n">
-        <v>-528</v>
+        <v>-531</v>
       </c>
       <c r="T30" s="1" t="n">
         <v>802</v>
@@ -2485,7 +2485,7 @@
       </c>
       <c r="X30" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\aeu.00037_19470820\aeu.00037_19470820.6.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\aeu.00037_19470820\aeu.00037_19470820.6.txt</t>
         </is>
       </c>
       <c r="Y30" s="1" t="n">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="Q31" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\aeu.00037_19470820\aeu.00037_19470820.7.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\aeu.00037_19470820\aeu.00037_19470820.7.txt</t>
         </is>
       </c>
       <c r="R31" s="1" t="n">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="X31" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\aeu.00037_19470820\aeu.00037_19470820.7.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\aeu.00037_19470820\aeu.00037_19470820.7.txt</t>
         </is>
       </c>
       <c r="Y31" s="1" t="n">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="Q32" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\aeu.00037_19470820\aeu.00037_19470820.8.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\aeu.00037_19470820\aeu.00037_19470820.8.txt</t>
         </is>
       </c>
       <c r="R32" s="1" t="n">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="X32" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\aeu.00037_19470820\aeu.00037_19470820.8.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\aeu.00037_19470820\aeu.00037_19470820.8.txt</t>
         </is>
       </c>
       <c r="Y32" s="1" t="n">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="Q33" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.1.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.1.txt</t>
         </is>
       </c>
       <c r="R33" s="1" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="X33" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0001.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0001.txt</t>
         </is>
       </c>
       <c r="Y33" s="1" t="n">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="Q34" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.10.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.10.txt</t>
         </is>
       </c>
       <c r="R34" s="1" t="n">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="X34" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0010.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0010.txt</t>
         </is>
       </c>
       <c r="Y34" s="1" t="n">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="Q35" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.100.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.100.txt</t>
         </is>
       </c>
       <c r="R35" s="1" t="n">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="X35" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0100.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0100.txt</t>
         </is>
       </c>
       <c r="Y35" s="1" t="n">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="Q36" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.101.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.101.txt</t>
         </is>
       </c>
       <c r="R36" s="1" t="n">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="X36" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0101.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0101.txt</t>
         </is>
       </c>
       <c r="Y36" s="1" t="n">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="Q37" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.102.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.102.txt</t>
         </is>
       </c>
       <c r="R37" s="1" t="n">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="X37" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0102.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0102.txt</t>
         </is>
       </c>
       <c r="Y37" s="1" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="Q38" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.103.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.103.txt</t>
         </is>
       </c>
       <c r="R38" s="1" t="n">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="X38" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0103.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0103.txt</t>
         </is>
       </c>
       <c r="Y38" s="1" t="n">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="Q39" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.104.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.104.txt</t>
         </is>
       </c>
       <c r="R39" s="1" t="n">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="X39" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0104.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0104.txt</t>
         </is>
       </c>
       <c r="Y39" s="1" t="n">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="Q40" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.105.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.105.txt</t>
         </is>
       </c>
       <c r="R40" s="1" t="n">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="X40" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0105.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0105.txt</t>
         </is>
       </c>
       <c r="Y40" s="1" t="n">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="Q41" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.106.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.106.txt</t>
         </is>
       </c>
       <c r="R41" s="1" t="n">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="X41" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0106.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0106.txt</t>
         </is>
       </c>
       <c r="Y41" s="1" t="n">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="Q42" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.107.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.107.txt</t>
         </is>
       </c>
       <c r="R42" s="1" t="n">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="X42" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0107.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0107.txt</t>
         </is>
       </c>
       <c r="Y42" s="1" t="n">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="Q43" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.108.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.108.txt</t>
         </is>
       </c>
       <c r="R43" s="1" t="n">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="X43" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0108.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0108.txt</t>
         </is>
       </c>
       <c r="Y43" s="1" t="n">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="Q44" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.109.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.109.txt</t>
         </is>
       </c>
       <c r="R44" s="1" t="n">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="X44" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0109.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0109.txt</t>
         </is>
       </c>
       <c r="Y44" s="1" t="n">
@@ -4063,7 +4063,7 @@
       </c>
       <c r="Q45" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.11.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.11.txt</t>
         </is>
       </c>
       <c r="R45" s="1" t="n">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="X45" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0011.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0011.txt</t>
         </is>
       </c>
       <c r="Y45" s="1" t="n">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="Q46" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.110.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.110.txt</t>
         </is>
       </c>
       <c r="R46" s="1" t="n">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="X46" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0110.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0110.txt</t>
         </is>
       </c>
       <c r="Y46" s="1" t="n">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="Q47" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.111.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.111.txt</t>
         </is>
       </c>
       <c r="R47" s="1" t="n">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="X47" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0111.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0111.txt</t>
         </is>
       </c>
       <c r="Y47" s="1" t="n">
@@ -4384,14 +4384,14 @@
       </c>
       <c r="Q48" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.112.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.112.txt</t>
         </is>
       </c>
       <c r="R48" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S48" s="1" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="T48" s="1" t="n">
         <v>122</v>
@@ -4411,7 +4411,7 @@
       </c>
       <c r="X48" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0112.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0112.txt</t>
         </is>
       </c>
       <c r="Y48" s="1" t="n">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="Q49" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.113.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.113.txt</t>
         </is>
       </c>
       <c r="R49" s="1" t="n">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="X49" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0113.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0113.txt</t>
         </is>
       </c>
       <c r="Y49" s="1" t="n">
@@ -4598,14 +4598,14 @@
       </c>
       <c r="Q50" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.114.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.114.txt</t>
         </is>
       </c>
       <c r="R50" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S50" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T50" s="1" t="n">
         <v>143</v>
@@ -4625,7 +4625,7 @@
       </c>
       <c r="X50" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0114.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0114.txt</t>
         </is>
       </c>
       <c r="Y50" s="1" t="n">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="Q51" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.115.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.115.txt</t>
         </is>
       </c>
       <c r="R51" s="1" t="n">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="X51" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0115.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0115.txt</t>
         </is>
       </c>
       <c r="Y51" s="1" t="n">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="Q52" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.116.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.116.txt</t>
         </is>
       </c>
       <c r="R52" s="1" t="n">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="X52" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0116.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0116.txt</t>
         </is>
       </c>
       <c r="Y52" s="1" t="n">
@@ -4919,7 +4919,7 @@
       </c>
       <c r="Q53" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.117.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.117.txt</t>
         </is>
       </c>
       <c r="R53" s="1" t="n">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="X53" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0117.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0117.txt</t>
         </is>
       </c>
       <c r="Y53" s="1" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="Q54" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.118.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.118.txt</t>
         </is>
       </c>
       <c r="R54" s="1" t="n">
@@ -5053,7 +5053,7 @@
       </c>
       <c r="X54" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0118.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0118.txt</t>
         </is>
       </c>
       <c r="Y54" s="1" t="n">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="Q55" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.119.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.119.txt</t>
         </is>
       </c>
       <c r="R55" s="1" t="n">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="X55" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0119.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0119.txt</t>
         </is>
       </c>
       <c r="Y55" s="1" t="n">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="Q56" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.12.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.12.txt</t>
         </is>
       </c>
       <c r="R56" s="1" t="n">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="X56" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0012.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0012.txt</t>
         </is>
       </c>
       <c r="Y56" s="1" t="n">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="Q57" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.120.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.120.txt</t>
         </is>
       </c>
       <c r="R57" s="1" t="n">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="X57" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0120.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0120.txt</t>
         </is>
       </c>
       <c r="Y57" s="1" t="n">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="Q58" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.121.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.121.txt</t>
         </is>
       </c>
       <c r="R58" s="1" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="X58" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0121.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0121.txt</t>
         </is>
       </c>
       <c r="Y58" s="1" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="Q59" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.122.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.122.txt</t>
         </is>
       </c>
       <c r="R59" s="1" t="n">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="X59" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0122.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0122.txt</t>
         </is>
       </c>
       <c r="Y59" s="1" t="n">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="Q60" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.123.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.123.txt</t>
         </is>
       </c>
       <c r="R60" s="1" t="n">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="X60" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0123.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0123.txt</t>
         </is>
       </c>
       <c r="Y60" s="1" t="n">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="Q61" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.124.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.124.txt</t>
         </is>
       </c>
       <c r="R61" s="1" t="n">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="X61" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0124.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0124.txt</t>
         </is>
       </c>
       <c r="Y61" s="1" t="n">
@@ -5882,7 +5882,7 @@
       </c>
       <c r="Q62" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.125.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.125.txt</t>
         </is>
       </c>
       <c r="R62" s="1" t="n">
@@ -5909,7 +5909,7 @@
       </c>
       <c r="X62" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0125.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0125.txt</t>
         </is>
       </c>
       <c r="Y62" s="1" t="n">
@@ -5989,7 +5989,7 @@
       </c>
       <c r="Q63" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.126.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.126.txt</t>
         </is>
       </c>
       <c r="R63" s="1" t="n">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="X63" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0126.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0126.txt</t>
         </is>
       </c>
       <c r="Y63" s="1" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="Q64" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.127.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.127.txt</t>
         </is>
       </c>
       <c r="R64" s="1" t="n">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="X64" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0127.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0127.txt</t>
         </is>
       </c>
       <c r="Y64" s="1" t="n">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="Q65" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.128.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.128.txt</t>
         </is>
       </c>
       <c r="R65" s="1" t="n">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="X65" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0128.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0128.txt</t>
         </is>
       </c>
       <c r="Y65" s="1" t="n">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="Q66" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.129.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.129.txt</t>
         </is>
       </c>
       <c r="R66" s="1" t="n">
@@ -6337,7 +6337,7 @@
       </c>
       <c r="X66" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0129.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0129.txt</t>
         </is>
       </c>
       <c r="Y66" s="1" t="n">
@@ -6417,7 +6417,7 @@
       </c>
       <c r="Q67" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.13.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.13.txt</t>
         </is>
       </c>
       <c r="R67" s="1" t="n">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="X67" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0013.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0013.txt</t>
         </is>
       </c>
       <c r="Y67" s="1" t="n">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="Q68" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.130.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.130.txt</t>
         </is>
       </c>
       <c r="R68" s="1" t="n">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="X68" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0130.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0130.txt</t>
         </is>
       </c>
       <c r="Y68" s="1" t="n">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="Q69" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.131.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.131.txt</t>
         </is>
       </c>
       <c r="R69" s="1" t="n">
@@ -6658,7 +6658,7 @@
       </c>
       <c r="X69" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0131.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0131.txt</t>
         </is>
       </c>
       <c r="Y69" s="1" t="n">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="Q70" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.132.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.132.txt</t>
         </is>
       </c>
       <c r="R70" s="1" t="n">
@@ -6765,7 +6765,7 @@
       </c>
       <c r="X70" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0132.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0132.txt</t>
         </is>
       </c>
       <c r="Y70" s="1" t="n">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="Q71" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.133.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.133.txt</t>
         </is>
       </c>
       <c r="R71" s="1" t="n">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="X71" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0133.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0133.txt</t>
         </is>
       </c>
       <c r="Y71" s="1" t="n">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="Q72" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.134.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.134.txt</t>
         </is>
       </c>
       <c r="R72" s="1" t="n">
@@ -6979,7 +6979,7 @@
       </c>
       <c r="X72" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0134.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0134.txt</t>
         </is>
       </c>
       <c r="Y72" s="1" t="n">
@@ -7059,14 +7059,14 @@
       </c>
       <c r="Q73" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.135.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.135.txt</t>
         </is>
       </c>
       <c r="R73" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S73" s="1" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T73" s="1" t="n">
         <v>157</v>
@@ -7086,7 +7086,7 @@
       </c>
       <c r="X73" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0135.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0135.txt</t>
         </is>
       </c>
       <c r="Y73" s="1" t="n">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="Q74" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.136.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.136.txt</t>
         </is>
       </c>
       <c r="R74" s="1" t="n">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="X74" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0136.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0136.txt</t>
         </is>
       </c>
       <c r="Y74" s="1" t="n">
@@ -7273,7 +7273,7 @@
       </c>
       <c r="Q75" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.137.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.137.txt</t>
         </is>
       </c>
       <c r="R75" s="1" t="n">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="X75" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0137.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0137.txt</t>
         </is>
       </c>
       <c r="Y75" s="1" t="n">
@@ -7380,7 +7380,7 @@
       </c>
       <c r="Q76" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.138.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.138.txt</t>
         </is>
       </c>
       <c r="R76" s="1" t="n">
@@ -7407,7 +7407,7 @@
       </c>
       <c r="X76" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0138.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0138.txt</t>
         </is>
       </c>
       <c r="Y76" s="1" t="n">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="Q77" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.139.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.139.txt</t>
         </is>
       </c>
       <c r="R77" s="1" t="n">
@@ -7514,7 +7514,7 @@
       </c>
       <c r="X77" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0139.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0139.txt</t>
         </is>
       </c>
       <c r="Y77" s="1" t="n">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="Q78" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.14.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.14.txt</t>
         </is>
       </c>
       <c r="R78" s="1" t="n">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="X78" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0014.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0014.txt</t>
         </is>
       </c>
       <c r="Y78" s="1" t="n">
@@ -7701,7 +7701,7 @@
       </c>
       <c r="Q79" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.140.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.140.txt</t>
         </is>
       </c>
       <c r="R79" s="1" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="X79" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0140.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0140.txt</t>
         </is>
       </c>
       <c r="Y79" s="1" t="n">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="Q80" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.141.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.141.txt</t>
         </is>
       </c>
       <c r="R80" s="1" t="n">
@@ -7835,7 +7835,7 @@
       </c>
       <c r="X80" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0141.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0141.txt</t>
         </is>
       </c>
       <c r="Y80" s="1" t="n">
@@ -7915,7 +7915,7 @@
       </c>
       <c r="Q81" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.142.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.142.txt</t>
         </is>
       </c>
       <c r="R81" s="1" t="n">
@@ -7942,7 +7942,7 @@
       </c>
       <c r="X81" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0142.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0142.txt</t>
         </is>
       </c>
       <c r="Y81" s="1" t="n">
@@ -8022,7 +8022,7 @@
       </c>
       <c r="Q82" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.143.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.143.txt</t>
         </is>
       </c>
       <c r="R82" s="1" t="n">
@@ -8049,7 +8049,7 @@
       </c>
       <c r="X82" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0143.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0143.txt</t>
         </is>
       </c>
       <c r="Y82" s="1" t="n">
@@ -8129,14 +8129,14 @@
       </c>
       <c r="Q83" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.144.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.144.txt</t>
         </is>
       </c>
       <c r="R83" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="S83" s="1" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="T83" s="1" t="n">
         <v>156</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="X83" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0144.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0144.txt</t>
         </is>
       </c>
       <c r="Y83" s="1" t="n">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="Q84" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.145.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.145.txt</t>
         </is>
       </c>
       <c r="R84" s="1" t="n">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="X84" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0145.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0145.txt</t>
         </is>
       </c>
       <c r="Y84" s="1" t="n">
@@ -8343,7 +8343,7 @@
       </c>
       <c r="Q85" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.146.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.146.txt</t>
         </is>
       </c>
       <c r="R85" s="1" t="n">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="X85" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0146.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0146.txt</t>
         </is>
       </c>
       <c r="Y85" s="1" t="n">
@@ -8450,7 +8450,7 @@
       </c>
       <c r="Q86" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.147.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.147.txt</t>
         </is>
       </c>
       <c r="R86" s="1" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="X86" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0147.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0147.txt</t>
         </is>
       </c>
       <c r="Y86" s="1" t="n">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="Q87" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.148.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.148.txt</t>
         </is>
       </c>
       <c r="R87" s="1" t="n">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="X87" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0148.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0148.txt</t>
         </is>
       </c>
       <c r="Y87" s="1" t="n">
@@ -8664,7 +8664,7 @@
       </c>
       <c r="Q88" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.149.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.149.txt</t>
         </is>
       </c>
       <c r="R88" s="1" t="n">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="X88" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0149.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0149.txt</t>
         </is>
       </c>
       <c r="Y88" s="1" t="n">
@@ -8771,14 +8771,14 @@
       </c>
       <c r="Q89" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.15.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.15.txt</t>
         </is>
       </c>
       <c r="R89" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S89" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T89" s="1" t="n">
         <v>141</v>
@@ -8798,7 +8798,7 @@
       </c>
       <c r="X89" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0015.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0015.txt</t>
         </is>
       </c>
       <c r="Y89" s="1" t="n">
@@ -8878,7 +8878,7 @@
       </c>
       <c r="Q90" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.150.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.150.txt</t>
         </is>
       </c>
       <c r="R90" s="1" t="n">
@@ -8905,7 +8905,7 @@
       </c>
       <c r="X90" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0150.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0150.txt</t>
         </is>
       </c>
       <c r="Y90" s="1" t="n">
@@ -8985,7 +8985,7 @@
       </c>
       <c r="Q91" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.151.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.151.txt</t>
         </is>
       </c>
       <c r="R91" s="1" t="n">
@@ -9012,7 +9012,7 @@
       </c>
       <c r="X91" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0151.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0151.txt</t>
         </is>
       </c>
       <c r="Y91" s="1" t="n">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="Q92" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.152.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.152.txt</t>
         </is>
       </c>
       <c r="R92" s="1" t="n">
@@ -9119,7 +9119,7 @@
       </c>
       <c r="X92" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0152.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0152.txt</t>
         </is>
       </c>
       <c r="Y92" s="1" t="n">
@@ -9199,7 +9199,7 @@
       </c>
       <c r="Q93" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.153.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.153.txt</t>
         </is>
       </c>
       <c r="R93" s="1" t="n">
@@ -9226,7 +9226,7 @@
       </c>
       <c r="X93" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0153.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0153.txt</t>
         </is>
       </c>
       <c r="Y93" s="1" t="n">
@@ -9306,7 +9306,7 @@
       </c>
       <c r="Q94" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.154.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.154.txt</t>
         </is>
       </c>
       <c r="R94" s="1" t="n">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="X94" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0154.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0154.txt</t>
         </is>
       </c>
       <c r="Y94" s="1" t="n">
@@ -9413,7 +9413,7 @@
       </c>
       <c r="Q95" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.155.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.155.txt</t>
         </is>
       </c>
       <c r="R95" s="1" t="n">
@@ -9440,7 +9440,7 @@
       </c>
       <c r="X95" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0155.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0155.txt</t>
         </is>
       </c>
       <c r="Y95" s="1" t="n">
@@ -9520,7 +9520,7 @@
       </c>
       <c r="Q96" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.156.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.156.txt</t>
         </is>
       </c>
       <c r="R96" s="1" t="n">
@@ -9547,7 +9547,7 @@
       </c>
       <c r="X96" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0156.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0156.txt</t>
         </is>
       </c>
       <c r="Y96" s="1" t="n">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="Q97" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.157.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.157.txt</t>
         </is>
       </c>
       <c r="R97" s="1" t="n">
@@ -9654,7 +9654,7 @@
       </c>
       <c r="X97" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0157.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0157.txt</t>
         </is>
       </c>
       <c r="Y97" s="1" t="n">
@@ -9734,7 +9734,7 @@
       </c>
       <c r="Q98" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.158.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.158.txt</t>
         </is>
       </c>
       <c r="R98" s="1" t="n">
@@ -9761,7 +9761,7 @@
       </c>
       <c r="X98" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0158.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0158.txt</t>
         </is>
       </c>
       <c r="Y98" s="1" t="n">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="Q99" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.159.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.159.txt</t>
         </is>
       </c>
       <c r="R99" s="1" t="n">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="X99" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0159.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0159.txt</t>
         </is>
       </c>
       <c r="Y99" s="1" t="n">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="Q100" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.16.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.16.txt</t>
         </is>
       </c>
       <c r="R100" s="1" t="n">
@@ -9975,7 +9975,7 @@
       </c>
       <c r="X100" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0016.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0016.txt</t>
         </is>
       </c>
       <c r="Y100" s="1" t="n">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="Q101" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.160.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.160.txt</t>
         </is>
       </c>
       <c r="R101" s="1" t="n">
@@ -10082,7 +10082,7 @@
       </c>
       <c r="X101" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0160.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0160.txt</t>
         </is>
       </c>
       <c r="Y101" s="1" t="n">
@@ -10162,7 +10162,7 @@
       </c>
       <c r="Q102" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.161.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.161.txt</t>
         </is>
       </c>
       <c r="R102" s="1" t="n">
@@ -10189,7 +10189,7 @@
       </c>
       <c r="X102" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0161.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0161.txt</t>
         </is>
       </c>
       <c r="Y102" s="1" t="n">
@@ -10269,7 +10269,7 @@
       </c>
       <c r="Q103" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.162.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.162.txt</t>
         </is>
       </c>
       <c r="R103" s="1" t="n">
@@ -10296,7 +10296,7 @@
       </c>
       <c r="X103" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0162.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0162.txt</t>
         </is>
       </c>
       <c r="Y103" s="1" t="n">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="Q104" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.163.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.163.txt</t>
         </is>
       </c>
       <c r="R104" s="1" t="n">
@@ -10403,7 +10403,7 @@
       </c>
       <c r="X104" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0163.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0163.txt</t>
         </is>
       </c>
       <c r="Y104" s="1" t="n">
@@ -10483,7 +10483,7 @@
       </c>
       <c r="Q105" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.164.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.164.txt</t>
         </is>
       </c>
       <c r="R105" s="1" t="n">
@@ -10510,7 +10510,7 @@
       </c>
       <c r="X105" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0164.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0164.txt</t>
         </is>
       </c>
       <c r="Y105" s="1" t="n">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="Q106" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.165.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.165.txt</t>
         </is>
       </c>
       <c r="R106" s="1" t="n">
@@ -10617,7 +10617,7 @@
       </c>
       <c r="X106" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0165.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0165.txt</t>
         </is>
       </c>
       <c r="Y106" s="1" t="n">
@@ -10697,7 +10697,7 @@
       </c>
       <c r="Q107" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.166.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.166.txt</t>
         </is>
       </c>
       <c r="R107" s="1" t="n">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="X107" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0166.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0166.txt</t>
         </is>
       </c>
       <c r="Y107" s="1" t="n">
@@ -10804,7 +10804,7 @@
       </c>
       <c r="Q108" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.167.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.167.txt</t>
         </is>
       </c>
       <c r="R108" s="1" t="n">
@@ -10831,7 +10831,7 @@
       </c>
       <c r="X108" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0167.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0167.txt</t>
         </is>
       </c>
       <c r="Y108" s="1" t="n">
@@ -10911,7 +10911,7 @@
       </c>
       <c r="Q109" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.168.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.168.txt</t>
         </is>
       </c>
       <c r="R109" s="1" t="n">
@@ -10938,7 +10938,7 @@
       </c>
       <c r="X109" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0168.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0168.txt</t>
         </is>
       </c>
       <c r="Y109" s="1" t="n">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="Q110" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.169.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.169.txt</t>
         </is>
       </c>
       <c r="R110" s="1" t="n">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="X110" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0169.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0169.txt</t>
         </is>
       </c>
       <c r="Y110" s="1" t="n">
@@ -11125,7 +11125,7 @@
       </c>
       <c r="Q111" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.17.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.17.txt</t>
         </is>
       </c>
       <c r="R111" s="1" t="n">
@@ -11152,7 +11152,7 @@
       </c>
       <c r="X111" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0017.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0017.txt</t>
         </is>
       </c>
       <c r="Y111" s="1" t="n">
@@ -11232,7 +11232,7 @@
       </c>
       <c r="Q112" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.170.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.170.txt</t>
         </is>
       </c>
       <c r="R112" s="1" t="n">
@@ -11259,7 +11259,7 @@
       </c>
       <c r="X112" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0170.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0170.txt</t>
         </is>
       </c>
       <c r="Y112" s="1" t="n">
@@ -11339,7 +11339,7 @@
       </c>
       <c r="Q113" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.171.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.171.txt</t>
         </is>
       </c>
       <c r="R113" s="1" t="n">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="X113" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0171.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0171.txt</t>
         </is>
       </c>
       <c r="Y113" s="1" t="n">
@@ -11446,7 +11446,7 @@
       </c>
       <c r="Q114" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.172.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.172.txt</t>
         </is>
       </c>
       <c r="R114" s="1" t="n">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="X114" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0172.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0172.txt</t>
         </is>
       </c>
       <c r="Y114" s="1" t="n">
@@ -11553,7 +11553,7 @@
       </c>
       <c r="Q115" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.173.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.173.txt</t>
         </is>
       </c>
       <c r="R115" s="1" t="n">
@@ -11580,7 +11580,7 @@
       </c>
       <c r="X115" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0173.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0173.txt</t>
         </is>
       </c>
       <c r="Y115" s="1" t="n">
@@ -11660,7 +11660,7 @@
       </c>
       <c r="Q116" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.174.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.174.txt</t>
         </is>
       </c>
       <c r="R116" s="1" t="n">
@@ -11687,7 +11687,7 @@
       </c>
       <c r="X116" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0174.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0174.txt</t>
         </is>
       </c>
       <c r="Y116" s="1" t="n">
@@ -11767,14 +11767,14 @@
       </c>
       <c r="Q117" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.175.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.175.txt</t>
         </is>
       </c>
       <c r="R117" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="S117" s="1" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="T117" s="1" t="n">
         <v>58</v>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="X117" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0175.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0175.txt</t>
         </is>
       </c>
       <c r="Y117" s="1" t="n">
@@ -11874,7 +11874,7 @@
       </c>
       <c r="Q118" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.176.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.176.txt</t>
         </is>
       </c>
       <c r="R118" s="1" t="n">
@@ -11901,7 +11901,7 @@
       </c>
       <c r="X118" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0176.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0176.txt</t>
         </is>
       </c>
       <c r="Y118" s="1" t="n">
@@ -11981,7 +11981,7 @@
       </c>
       <c r="Q119" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.177.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.177.txt</t>
         </is>
       </c>
       <c r="R119" s="1" t="n">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="X119" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0177.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0177.txt</t>
         </is>
       </c>
       <c r="Y119" s="1" t="n">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="Q120" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.18.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.18.txt</t>
         </is>
       </c>
       <c r="R120" s="1" t="n">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="X120" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0018.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0018.txt</t>
         </is>
       </c>
       <c r="Y120" s="1" t="n">
@@ -12195,7 +12195,7 @@
       </c>
       <c r="Q121" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.19.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.19.txt</t>
         </is>
       </c>
       <c r="R121" s="1" t="n">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="X121" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0019.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0019.txt</t>
         </is>
       </c>
       <c r="Y121" s="1" t="n">
@@ -12302,7 +12302,7 @@
       </c>
       <c r="Q122" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.2.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.2.txt</t>
         </is>
       </c>
       <c r="R122" s="1" t="n">
@@ -12329,7 +12329,7 @@
       </c>
       <c r="X122" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0002.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0002.txt</t>
         </is>
       </c>
       <c r="Y122" s="1" t="n">
@@ -12409,7 +12409,7 @@
       </c>
       <c r="Q123" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.20.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.20.txt</t>
         </is>
       </c>
       <c r="R123" s="1" t="n">
@@ -12436,7 +12436,7 @@
       </c>
       <c r="X123" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0020.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0020.txt</t>
         </is>
       </c>
       <c r="Y123" s="1" t="n">
@@ -12516,7 +12516,7 @@
       </c>
       <c r="Q124" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.21.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.21.txt</t>
         </is>
       </c>
       <c r="R124" s="1" t="n">
@@ -12543,7 +12543,7 @@
       </c>
       <c r="X124" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0021.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0021.txt</t>
         </is>
       </c>
       <c r="Y124" s="1" t="n">
@@ -12623,7 +12623,7 @@
       </c>
       <c r="Q125" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.22.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.22.txt</t>
         </is>
       </c>
       <c r="R125" s="1" t="n">
@@ -12650,7 +12650,7 @@
       </c>
       <c r="X125" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0022.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0022.txt</t>
         </is>
       </c>
       <c r="Y125" s="1" t="n">
@@ -12730,7 +12730,7 @@
       </c>
       <c r="Q126" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.23.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.23.txt</t>
         </is>
       </c>
       <c r="R126" s="1" t="n">
@@ -12757,7 +12757,7 @@
       </c>
       <c r="X126" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0023.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0023.txt</t>
         </is>
       </c>
       <c r="Y126" s="1" t="n">
@@ -12837,7 +12837,7 @@
       </c>
       <c r="Q127" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.24.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.24.txt</t>
         </is>
       </c>
       <c r="R127" s="1" t="n">
@@ -12864,7 +12864,7 @@
       </c>
       <c r="X127" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0024.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0024.txt</t>
         </is>
       </c>
       <c r="Y127" s="1" t="n">
@@ -12944,7 +12944,7 @@
       </c>
       <c r="Q128" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.25.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.25.txt</t>
         </is>
       </c>
       <c r="R128" s="1" t="n">
@@ -12971,7 +12971,7 @@
       </c>
       <c r="X128" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0025.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0025.txt</t>
         </is>
       </c>
       <c r="Y128" s="1" t="n">
@@ -13051,7 +13051,7 @@
       </c>
       <c r="Q129" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.26.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.26.txt</t>
         </is>
       </c>
       <c r="R129" s="1" t="n">
@@ -13078,7 +13078,7 @@
       </c>
       <c r="X129" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0026.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0026.txt</t>
         </is>
       </c>
       <c r="Y129" s="1" t="n">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="Q130" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.27.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.27.txt</t>
         </is>
       </c>
       <c r="R130" s="1" t="n">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="X130" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0027.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0027.txt</t>
         </is>
       </c>
       <c r="Y130" s="1" t="n">
@@ -13265,14 +13265,14 @@
       </c>
       <c r="Q131" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.28.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.28.txt</t>
         </is>
       </c>
       <c r="R131" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S131" s="1" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="T131" s="1" t="n">
         <v>64</v>
@@ -13292,7 +13292,7 @@
       </c>
       <c r="X131" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0028.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0028.txt</t>
         </is>
       </c>
       <c r="Y131" s="1" t="n">
@@ -13372,14 +13372,14 @@
       </c>
       <c r="Q132" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.29.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.29.txt</t>
         </is>
       </c>
       <c r="R132" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S132" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T132" s="1" t="n">
         <v>143</v>
@@ -13399,7 +13399,7 @@
       </c>
       <c r="X132" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0029.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0029.txt</t>
         </is>
       </c>
       <c r="Y132" s="1" t="n">
@@ -13479,14 +13479,14 @@
       </c>
       <c r="Q133" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.3.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.3.txt</t>
         </is>
       </c>
       <c r="R133" s="1" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S133" s="1" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="T133" s="1" t="n">
         <v>202</v>
@@ -13506,7 +13506,7 @@
       </c>
       <c r="X133" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0003.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0003.txt</t>
         </is>
       </c>
       <c r="Y133" s="1" t="n">
@@ -13586,7 +13586,7 @@
       </c>
       <c r="Q134" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.30.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.30.txt</t>
         </is>
       </c>
       <c r="R134" s="1" t="n">
@@ -13613,7 +13613,7 @@
       </c>
       <c r="X134" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0030.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0030.txt</t>
         </is>
       </c>
       <c r="Y134" s="1" t="n">
@@ -13693,7 +13693,7 @@
       </c>
       <c r="Q135" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.31.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.31.txt</t>
         </is>
       </c>
       <c r="R135" s="1" t="n">
@@ -13720,7 +13720,7 @@
       </c>
       <c r="X135" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0031.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0031.txt</t>
         </is>
       </c>
       <c r="Y135" s="1" t="n">
@@ -13800,7 +13800,7 @@
       </c>
       <c r="Q136" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.32.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.32.txt</t>
         </is>
       </c>
       <c r="R136" s="1" t="n">
@@ -13827,7 +13827,7 @@
       </c>
       <c r="X136" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0032.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0032.txt</t>
         </is>
       </c>
       <c r="Y136" s="1" t="n">
@@ -13907,7 +13907,7 @@
       </c>
       <c r="Q137" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.33.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.33.txt</t>
         </is>
       </c>
       <c r="R137" s="1" t="n">
@@ -13934,7 +13934,7 @@
       </c>
       <c r="X137" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0033.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0033.txt</t>
         </is>
       </c>
       <c r="Y137" s="1" t="n">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="Q138" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.34.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.34.txt</t>
         </is>
       </c>
       <c r="R138" s="1" t="n">
@@ -14041,7 +14041,7 @@
       </c>
       <c r="X138" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0034.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0034.txt</t>
         </is>
       </c>
       <c r="Y138" s="1" t="n">
@@ -14121,7 +14121,7 @@
       </c>
       <c r="Q139" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.35.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.35.txt</t>
         </is>
       </c>
       <c r="R139" s="1" t="n">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="X139" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0035.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0035.txt</t>
         </is>
       </c>
       <c r="Y139" s="1" t="n">
@@ -14228,7 +14228,7 @@
       </c>
       <c r="Q140" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.36.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.36.txt</t>
         </is>
       </c>
       <c r="R140" s="1" t="n">
@@ -14255,7 +14255,7 @@
       </c>
       <c r="X140" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0036.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0036.txt</t>
         </is>
       </c>
       <c r="Y140" s="1" t="n">
@@ -14335,7 +14335,7 @@
       </c>
       <c r="Q141" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.37.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.37.txt</t>
         </is>
       </c>
       <c r="R141" s="1" t="n">
@@ -14362,7 +14362,7 @@
       </c>
       <c r="X141" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0037.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0037.txt</t>
         </is>
       </c>
       <c r="Y141" s="1" t="n">
@@ -14442,7 +14442,7 @@
       </c>
       <c r="Q142" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.38.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.38.txt</t>
         </is>
       </c>
       <c r="R142" s="1" t="n">
@@ -14469,7 +14469,7 @@
       </c>
       <c r="X142" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0038.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0038.txt</t>
         </is>
       </c>
       <c r="Y142" s="1" t="n">
@@ -14549,7 +14549,7 @@
       </c>
       <c r="Q143" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.39.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.39.txt</t>
         </is>
       </c>
       <c r="R143" s="1" t="n">
@@ -14576,7 +14576,7 @@
       </c>
       <c r="X143" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0039.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0039.txt</t>
         </is>
       </c>
       <c r="Y143" s="1" t="n">
@@ -14656,7 +14656,7 @@
       </c>
       <c r="Q144" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.4.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.4.txt</t>
         </is>
       </c>
       <c r="R144" s="1" t="n">
@@ -14683,7 +14683,7 @@
       </c>
       <c r="X144" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0004.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0004.txt</t>
         </is>
       </c>
       <c r="Y144" s="1" t="n">
@@ -14763,7 +14763,7 @@
       </c>
       <c r="Q145" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.40.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.40.txt</t>
         </is>
       </c>
       <c r="R145" s="1" t="n">
@@ -14790,7 +14790,7 @@
       </c>
       <c r="X145" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0040.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0040.txt</t>
         </is>
       </c>
       <c r="Y145" s="1" t="n">
@@ -14870,7 +14870,7 @@
       </c>
       <c r="Q146" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.41.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.41.txt</t>
         </is>
       </c>
       <c r="R146" s="1" t="n">
@@ -14897,7 +14897,7 @@
       </c>
       <c r="X146" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0041.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0041.txt</t>
         </is>
       </c>
       <c r="Y146" s="1" t="n">
@@ -14977,7 +14977,7 @@
       </c>
       <c r="Q147" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.42.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.42.txt</t>
         </is>
       </c>
       <c r="R147" s="1" t="n">
@@ -15004,7 +15004,7 @@
       </c>
       <c r="X147" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0042.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0042.txt</t>
         </is>
       </c>
       <c r="Y147" s="1" t="n">
@@ -15084,7 +15084,7 @@
       </c>
       <c r="Q148" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.43.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.43.txt</t>
         </is>
       </c>
       <c r="R148" s="1" t="n">
@@ -15111,7 +15111,7 @@
       </c>
       <c r="X148" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0043.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0043.txt</t>
         </is>
       </c>
       <c r="Y148" s="1" t="n">
@@ -15191,7 +15191,7 @@
       </c>
       <c r="Q149" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.44.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.44.txt</t>
         </is>
       </c>
       <c r="R149" s="1" t="n">
@@ -15218,7 +15218,7 @@
       </c>
       <c r="X149" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0044.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0044.txt</t>
         </is>
       </c>
       <c r="Y149" s="1" t="n">
@@ -15298,7 +15298,7 @@
       </c>
       <c r="Q150" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.45.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.45.txt</t>
         </is>
       </c>
       <c r="R150" s="1" t="n">
@@ -15325,7 +15325,7 @@
       </c>
       <c r="X150" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0045.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0045.txt</t>
         </is>
       </c>
       <c r="Y150" s="1" t="n">
@@ -15405,7 +15405,7 @@
       </c>
       <c r="Q151" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.46.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.46.txt</t>
         </is>
       </c>
       <c r="R151" s="1" t="n">
@@ -15432,7 +15432,7 @@
       </c>
       <c r="X151" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0046.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0046.txt</t>
         </is>
       </c>
       <c r="Y151" s="1" t="n">
@@ -15512,7 +15512,7 @@
       </c>
       <c r="Q152" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.47.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.47.txt</t>
         </is>
       </c>
       <c r="R152" s="1" t="n">
@@ -15539,7 +15539,7 @@
       </c>
       <c r="X152" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0047.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0047.txt</t>
         </is>
       </c>
       <c r="Y152" s="1" t="n">
@@ -15619,7 +15619,7 @@
       </c>
       <c r="Q153" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.48.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.48.txt</t>
         </is>
       </c>
       <c r="R153" s="1" t="n">
@@ -15646,7 +15646,7 @@
       </c>
       <c r="X153" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0048.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0048.txt</t>
         </is>
       </c>
       <c r="Y153" s="1" t="n">
@@ -15726,7 +15726,7 @@
       </c>
       <c r="Q154" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.49.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.49.txt</t>
         </is>
       </c>
       <c r="R154" s="1" t="n">
@@ -15753,7 +15753,7 @@
       </c>
       <c r="X154" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0049.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0049.txt</t>
         </is>
       </c>
       <c r="Y154" s="1" t="n">
@@ -15833,7 +15833,7 @@
       </c>
       <c r="Q155" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.5.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.5.txt</t>
         </is>
       </c>
       <c r="R155" s="1" t="n">
@@ -15860,7 +15860,7 @@
       </c>
       <c r="X155" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0005.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0005.txt</t>
         </is>
       </c>
       <c r="Y155" s="1" t="n">
@@ -15940,7 +15940,7 @@
       </c>
       <c r="Q156" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.50.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.50.txt</t>
         </is>
       </c>
       <c r="R156" s="1" t="n">
@@ -15967,7 +15967,7 @@
       </c>
       <c r="X156" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0050.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0050.txt</t>
         </is>
       </c>
       <c r="Y156" s="1" t="n">
@@ -16047,7 +16047,7 @@
       </c>
       <c r="Q157" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.51.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.51.txt</t>
         </is>
       </c>
       <c r="R157" s="1" t="n">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="X157" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0051.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0051.txt</t>
         </is>
       </c>
       <c r="Y157" s="1" t="n">
@@ -16154,7 +16154,7 @@
       </c>
       <c r="Q158" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.52.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.52.txt</t>
         </is>
       </c>
       <c r="R158" s="1" t="n">
@@ -16181,7 +16181,7 @@
       </c>
       <c r="X158" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0052.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0052.txt</t>
         </is>
       </c>
       <c r="Y158" s="1" t="n">
@@ -16261,7 +16261,7 @@
       </c>
       <c r="Q159" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.53.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.53.txt</t>
         </is>
       </c>
       <c r="R159" s="1" t="n">
@@ -16288,7 +16288,7 @@
       </c>
       <c r="X159" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0053.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0053.txt</t>
         </is>
       </c>
       <c r="Y159" s="1" t="n">
@@ -16368,7 +16368,7 @@
       </c>
       <c r="Q160" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.54.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.54.txt</t>
         </is>
       </c>
       <c r="R160" s="1" t="n">
@@ -16395,7 +16395,7 @@
       </c>
       <c r="X160" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0054.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0054.txt</t>
         </is>
       </c>
       <c r="Y160" s="1" t="n">
@@ -16475,7 +16475,7 @@
       </c>
       <c r="Q161" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.55.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.55.txt</t>
         </is>
       </c>
       <c r="R161" s="1" t="n">
@@ -16502,7 +16502,7 @@
       </c>
       <c r="X161" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0055.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0055.txt</t>
         </is>
       </c>
       <c r="Y161" s="1" t="n">
@@ -16582,7 +16582,7 @@
       </c>
       <c r="Q162" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.56.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.56.txt</t>
         </is>
       </c>
       <c r="R162" s="1" t="n">
@@ -16609,7 +16609,7 @@
       </c>
       <c r="X162" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0056.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0056.txt</t>
         </is>
       </c>
       <c r="Y162" s="1" t="n">
@@ -16689,14 +16689,14 @@
       </c>
       <c r="Q163" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.57.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.57.txt</t>
         </is>
       </c>
       <c r="R163" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S163" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T163" s="1" t="n">
         <v>154</v>
@@ -16716,7 +16716,7 @@
       </c>
       <c r="X163" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0057.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0057.txt</t>
         </is>
       </c>
       <c r="Y163" s="1" t="n">
@@ -16796,7 +16796,7 @@
       </c>
       <c r="Q164" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.58.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.58.txt</t>
         </is>
       </c>
       <c r="R164" s="1" t="n">
@@ -16823,7 +16823,7 @@
       </c>
       <c r="X164" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0058.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0058.txt</t>
         </is>
       </c>
       <c r="Y164" s="1" t="n">
@@ -16903,7 +16903,7 @@
       </c>
       <c r="Q165" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.59.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.59.txt</t>
         </is>
       </c>
       <c r="R165" s="1" t="n">
@@ -16930,7 +16930,7 @@
       </c>
       <c r="X165" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0059.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0059.txt</t>
         </is>
       </c>
       <c r="Y165" s="1" t="n">
@@ -17010,7 +17010,7 @@
       </c>
       <c r="Q166" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.6.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.6.txt</t>
         </is>
       </c>
       <c r="R166" s="1" t="n">
@@ -17037,7 +17037,7 @@
       </c>
       <c r="X166" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0006.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0006.txt</t>
         </is>
       </c>
       <c r="Y166" s="1" t="n">
@@ -17117,7 +17117,7 @@
       </c>
       <c r="Q167" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.60.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.60.txt</t>
         </is>
       </c>
       <c r="R167" s="1" t="n">
@@ -17144,7 +17144,7 @@
       </c>
       <c r="X167" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0060.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0060.txt</t>
         </is>
       </c>
       <c r="Y167" s="1" t="n">
@@ -17224,7 +17224,7 @@
       </c>
       <c r="Q168" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.61.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.61.txt</t>
         </is>
       </c>
       <c r="R168" s="1" t="n">
@@ -17251,7 +17251,7 @@
       </c>
       <c r="X168" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0061.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0061.txt</t>
         </is>
       </c>
       <c r="Y168" s="1" t="n">
@@ -17331,7 +17331,7 @@
       </c>
       <c r="Q169" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.62.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.62.txt</t>
         </is>
       </c>
       <c r="R169" s="1" t="n">
@@ -17358,7 +17358,7 @@
       </c>
       <c r="X169" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0062.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0062.txt</t>
         </is>
       </c>
       <c r="Y169" s="1" t="n">
@@ -17438,7 +17438,7 @@
       </c>
       <c r="Q170" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.63.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.63.txt</t>
         </is>
       </c>
       <c r="R170" s="1" t="n">
@@ -17465,7 +17465,7 @@
       </c>
       <c r="X170" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0063.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0063.txt</t>
         </is>
       </c>
       <c r="Y170" s="1" t="n">
@@ -17545,7 +17545,7 @@
       </c>
       <c r="Q171" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.64.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.64.txt</t>
         </is>
       </c>
       <c r="R171" s="1" t="n">
@@ -17572,7 +17572,7 @@
       </c>
       <c r="X171" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0064.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0064.txt</t>
         </is>
       </c>
       <c r="Y171" s="1" t="n">
@@ -17652,7 +17652,7 @@
       </c>
       <c r="Q172" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.65.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.65.txt</t>
         </is>
       </c>
       <c r="R172" s="1" t="n">
@@ -17679,7 +17679,7 @@
       </c>
       <c r="X172" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0065.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0065.txt</t>
         </is>
       </c>
       <c r="Y172" s="1" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="Q173" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.66.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.66.txt</t>
         </is>
       </c>
       <c r="R173" s="1" t="n">
@@ -17786,7 +17786,7 @@
       </c>
       <c r="X173" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0066.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0066.txt</t>
         </is>
       </c>
       <c r="Y173" s="1" t="n">
@@ -17866,7 +17866,7 @@
       </c>
       <c r="Q174" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.67.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.67.txt</t>
         </is>
       </c>
       <c r="R174" s="1" t="n">
@@ -17893,7 +17893,7 @@
       </c>
       <c r="X174" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0067.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0067.txt</t>
         </is>
       </c>
       <c r="Y174" s="1" t="n">
@@ -17973,7 +17973,7 @@
       </c>
       <c r="Q175" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.68.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.68.txt</t>
         </is>
       </c>
       <c r="R175" s="1" t="n">
@@ -18000,7 +18000,7 @@
       </c>
       <c r="X175" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0068.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0068.txt</t>
         </is>
       </c>
       <c r="Y175" s="1" t="n">
@@ -18080,7 +18080,7 @@
       </c>
       <c r="Q176" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.69.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.69.txt</t>
         </is>
       </c>
       <c r="R176" s="1" t="n">
@@ -18107,7 +18107,7 @@
       </c>
       <c r="X176" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0069.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0069.txt</t>
         </is>
       </c>
       <c r="Y176" s="1" t="n">
@@ -18187,7 +18187,7 @@
       </c>
       <c r="Q177" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.7.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.7.txt</t>
         </is>
       </c>
       <c r="R177" s="1" t="n">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="X177" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0007.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0007.txt</t>
         </is>
       </c>
       <c r="Y177" s="1" t="n">
@@ -18294,7 +18294,7 @@
       </c>
       <c r="Q178" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.70.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.70.txt</t>
         </is>
       </c>
       <c r="R178" s="1" t="n">
@@ -18321,7 +18321,7 @@
       </c>
       <c r="X178" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0070.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0070.txt</t>
         </is>
       </c>
       <c r="Y178" s="1" t="n">
@@ -18401,7 +18401,7 @@
       </c>
       <c r="Q179" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.71.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.71.txt</t>
         </is>
       </c>
       <c r="R179" s="1" t="n">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="X179" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0071.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0071.txt</t>
         </is>
       </c>
       <c r="Y179" s="1" t="n">
@@ -18508,7 +18508,7 @@
       </c>
       <c r="Q180" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.72.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.72.txt</t>
         </is>
       </c>
       <c r="R180" s="1" t="n">
@@ -18535,7 +18535,7 @@
       </c>
       <c r="X180" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0072.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0072.txt</t>
         </is>
       </c>
       <c r="Y180" s="1" t="n">
@@ -18615,7 +18615,7 @@
       </c>
       <c r="Q181" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.73.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.73.txt</t>
         </is>
       </c>
       <c r="R181" s="1" t="n">
@@ -18642,7 +18642,7 @@
       </c>
       <c r="X181" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0073.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0073.txt</t>
         </is>
       </c>
       <c r="Y181" s="1" t="n">
@@ -18722,7 +18722,7 @@
       </c>
       <c r="Q182" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.74.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.74.txt</t>
         </is>
       </c>
       <c r="R182" s="1" t="n">
@@ -18749,7 +18749,7 @@
       </c>
       <c r="X182" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0074.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0074.txt</t>
         </is>
       </c>
       <c r="Y182" s="1" t="n">
@@ -18829,7 +18829,7 @@
       </c>
       <c r="Q183" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.75.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.75.txt</t>
         </is>
       </c>
       <c r="R183" s="1" t="n">
@@ -18856,7 +18856,7 @@
       </c>
       <c r="X183" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0075.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0075.txt</t>
         </is>
       </c>
       <c r="Y183" s="1" t="n">
@@ -18936,7 +18936,7 @@
       </c>
       <c r="Q184" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.76.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.76.txt</t>
         </is>
       </c>
       <c r="R184" s="1" t="n">
@@ -18963,7 +18963,7 @@
       </c>
       <c r="X184" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0076.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0076.txt</t>
         </is>
       </c>
       <c r="Y184" s="1" t="n">
@@ -19043,7 +19043,7 @@
       </c>
       <c r="Q185" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.77.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.77.txt</t>
         </is>
       </c>
       <c r="R185" s="1" t="n">
@@ -19070,7 +19070,7 @@
       </c>
       <c r="X185" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0077.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0077.txt</t>
         </is>
       </c>
       <c r="Y185" s="1" t="n">
@@ -19150,7 +19150,7 @@
       </c>
       <c r="Q186" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.78.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.78.txt</t>
         </is>
       </c>
       <c r="R186" s="1" t="n">
@@ -19177,7 +19177,7 @@
       </c>
       <c r="X186" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0078.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0078.txt</t>
         </is>
       </c>
       <c r="Y186" s="1" t="n">
@@ -19257,7 +19257,7 @@
       </c>
       <c r="Q187" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.79.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.79.txt</t>
         </is>
       </c>
       <c r="R187" s="1" t="n">
@@ -19284,7 +19284,7 @@
       </c>
       <c r="X187" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0079.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0079.txt</t>
         </is>
       </c>
       <c r="Y187" s="1" t="n">
@@ -19364,14 +19364,14 @@
       </c>
       <c r="Q188" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.8.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.8.txt</t>
         </is>
       </c>
       <c r="R188" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S188" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T188" s="1" t="n">
         <v>31</v>
@@ -19391,7 +19391,7 @@
       </c>
       <c r="X188" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0008.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0008.txt</t>
         </is>
       </c>
       <c r="Y188" s="1" t="n">
@@ -19471,7 +19471,7 @@
       </c>
       <c r="Q189" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.80.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.80.txt</t>
         </is>
       </c>
       <c r="R189" s="1" t="n">
@@ -19498,7 +19498,7 @@
       </c>
       <c r="X189" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0080.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0080.txt</t>
         </is>
       </c>
       <c r="Y189" s="1" t="n">
@@ -19578,7 +19578,7 @@
       </c>
       <c r="Q190" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.81.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.81.txt</t>
         </is>
       </c>
       <c r="R190" s="1" t="n">
@@ -19605,7 +19605,7 @@
       </c>
       <c r="X190" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0081.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0081.txt</t>
         </is>
       </c>
       <c r="Y190" s="1" t="n">
@@ -19685,7 +19685,7 @@
       </c>
       <c r="Q191" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.82.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.82.txt</t>
         </is>
       </c>
       <c r="R191" s="1" t="n">
@@ -19712,7 +19712,7 @@
       </c>
       <c r="X191" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0082.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0082.txt</t>
         </is>
       </c>
       <c r="Y191" s="1" t="n">
@@ -19792,7 +19792,7 @@
       </c>
       <c r="Q192" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.83.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.83.txt</t>
         </is>
       </c>
       <c r="R192" s="1" t="n">
@@ -19819,7 +19819,7 @@
       </c>
       <c r="X192" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0083.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0083.txt</t>
         </is>
       </c>
       <c r="Y192" s="1" t="n">
@@ -19899,7 +19899,7 @@
       </c>
       <c r="Q193" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.84.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.84.txt</t>
         </is>
       </c>
       <c r="R193" s="1" t="n">
@@ -19926,7 +19926,7 @@
       </c>
       <c r="X193" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0084.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0084.txt</t>
         </is>
       </c>
       <c r="Y193" s="1" t="n">
@@ -20006,7 +20006,7 @@
       </c>
       <c r="Q194" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.85.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.85.txt</t>
         </is>
       </c>
       <c r="R194" s="1" t="n">
@@ -20033,7 +20033,7 @@
       </c>
       <c r="X194" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0085.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0085.txt</t>
         </is>
       </c>
       <c r="Y194" s="1" t="n">
@@ -20113,14 +20113,14 @@
       </c>
       <c r="Q195" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.86.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.86.txt</t>
         </is>
       </c>
       <c r="R195" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S195" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T195" s="1" t="n">
         <v>146</v>
@@ -20140,7 +20140,7 @@
       </c>
       <c r="X195" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0086.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0086.txt</t>
         </is>
       </c>
       <c r="Y195" s="1" t="n">
@@ -20220,7 +20220,7 @@
       </c>
       <c r="Q196" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.87.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.87.txt</t>
         </is>
       </c>
       <c r="R196" s="1" t="n">
@@ -20247,7 +20247,7 @@
       </c>
       <c r="X196" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0087.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0087.txt</t>
         </is>
       </c>
       <c r="Y196" s="1" t="n">
@@ -20327,7 +20327,7 @@
       </c>
       <c r="Q197" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.88.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.88.txt</t>
         </is>
       </c>
       <c r="R197" s="1" t="n">
@@ -20354,7 +20354,7 @@
       </c>
       <c r="X197" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0088.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0088.txt</t>
         </is>
       </c>
       <c r="Y197" s="1" t="n">
@@ -20434,7 +20434,7 @@
       </c>
       <c r="Q198" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.89.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.89.txt</t>
         </is>
       </c>
       <c r="R198" s="1" t="n">
@@ -20461,7 +20461,7 @@
       </c>
       <c r="X198" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0089.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0089.txt</t>
         </is>
       </c>
       <c r="Y198" s="1" t="n">
@@ -20541,7 +20541,7 @@
       </c>
       <c r="Q199" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.9.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.9.txt</t>
         </is>
       </c>
       <c r="R199" s="1" t="n">
@@ -20568,7 +20568,7 @@
       </c>
       <c r="X199" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0009.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0009.txt</t>
         </is>
       </c>
       <c r="Y199" s="1" t="n">
@@ -20648,7 +20648,7 @@
       </c>
       <c r="Q200" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.90.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.90.txt</t>
         </is>
       </c>
       <c r="R200" s="1" t="n">
@@ -20675,7 +20675,7 @@
       </c>
       <c r="X200" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0090.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0090.txt</t>
         </is>
       </c>
       <c r="Y200" s="1" t="n">
@@ -20755,7 +20755,7 @@
       </c>
       <c r="Q201" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.91.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.91.txt</t>
         </is>
       </c>
       <c r="R201" s="1" t="n">
@@ -20782,7 +20782,7 @@
       </c>
       <c r="X201" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0091.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0091.txt</t>
         </is>
       </c>
       <c r="Y201" s="1" t="n">
@@ -20862,7 +20862,7 @@
       </c>
       <c r="Q202" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.92.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.92.txt</t>
         </is>
       </c>
       <c r="R202" s="1" t="n">
@@ -20889,7 +20889,7 @@
       </c>
       <c r="X202" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0092.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0092.txt</t>
         </is>
       </c>
       <c r="Y202" s="1" t="n">
@@ -20969,7 +20969,7 @@
       </c>
       <c r="Q203" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.93.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.93.txt</t>
         </is>
       </c>
       <c r="R203" s="1" t="n">
@@ -20996,7 +20996,7 @@
       </c>
       <c r="X203" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0093.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0093.txt</t>
         </is>
       </c>
       <c r="Y203" s="1" t="n">
@@ -21076,7 +21076,7 @@
       </c>
       <c r="Q204" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.94.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.94.txt</t>
         </is>
       </c>
       <c r="R204" s="1" t="n">
@@ -21103,7 +21103,7 @@
       </c>
       <c r="X204" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0094.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0094.txt</t>
         </is>
       </c>
       <c r="Y204" s="1" t="n">
@@ -21183,7 +21183,7 @@
       </c>
       <c r="Q205" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.95.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.95.txt</t>
         </is>
       </c>
       <c r="R205" s="1" t="n">
@@ -21210,7 +21210,7 @@
       </c>
       <c r="X205" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0095.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0095.txt</t>
         </is>
       </c>
       <c r="Y205" s="1" t="n">
@@ -21290,7 +21290,7 @@
       </c>
       <c r="Q206" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.96.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.96.txt</t>
         </is>
       </c>
       <c r="R206" s="1" t="n">
@@ -21317,7 +21317,7 @@
       </c>
       <c r="X206" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0096.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0096.txt</t>
         </is>
       </c>
       <c r="Y206" s="1" t="n">
@@ -21397,7 +21397,7 @@
       </c>
       <c r="Q207" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.97.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.97.txt</t>
         </is>
       </c>
       <c r="R207" s="1" t="n">
@@ -21424,7 +21424,7 @@
       </c>
       <c r="X207" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0097.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0097.txt</t>
         </is>
       </c>
       <c r="Y207" s="1" t="n">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="Q208" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.98.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.98.txt</t>
         </is>
       </c>
       <c r="R208" s="1" t="n">
@@ -21531,7 +21531,7 @@
       </c>
       <c r="X208" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0098.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0098.txt</t>
         </is>
       </c>
       <c r="Y208" s="1" t="n">
@@ -21611,7 +21611,7 @@
       </c>
       <c r="Q209" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.99.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.99.txt</t>
         </is>
       </c>
       <c r="R209" s="1" t="n">
@@ -21638,7 +21638,7 @@
       </c>
       <c r="X209" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0099.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0099.txt</t>
         </is>
       </c>
       <c r="Y209" s="1" t="n">
@@ -21718,14 +21718,14 @@
       </c>
       <c r="Q210" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00126_19130805\oocihm.N_00126_19130805.1.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00126_19130805\oocihm.N_00126_19130805.1.txt</t>
         </is>
       </c>
       <c r="R210" s="1" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="S210" s="1" t="n">
-        <v>-53</v>
+        <v>-55</v>
       </c>
       <c r="T210" s="1" t="n">
         <v>820</v>
@@ -21745,7 +21745,7 @@
       </c>
       <c r="X210" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.1.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.1.txt</t>
         </is>
       </c>
       <c r="Y210" s="1" t="n">
@@ -21825,7 +21825,7 @@
       </c>
       <c r="Q211" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00126_19130805\oocihm.N_00126_19130805.2.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00126_19130805\oocihm.N_00126_19130805.2.txt</t>
         </is>
       </c>
       <c r="R211" s="1" t="n">
@@ -21852,7 +21852,7 @@
       </c>
       <c r="X211" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.2.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.2.txt</t>
         </is>
       </c>
       <c r="Y211" s="1" t="n">
@@ -21932,14 +21932,14 @@
       </c>
       <c r="Q212" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00126_19130805\oocihm.N_00126_19130805.3.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00126_19130805\oocihm.N_00126_19130805.3.txt</t>
         </is>
       </c>
       <c r="R212" s="1" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S212" s="1" t="n">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="T212" s="1" t="n">
         <v>595</v>
@@ -21959,7 +21959,7 @@
       </c>
       <c r="X212" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.3.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.3.txt</t>
         </is>
       </c>
       <c r="Y212" s="1" t="n">
@@ -22039,7 +22039,7 @@
       </c>
       <c r="Q213" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00126_19130805\oocihm.N_00126_19130805.4.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00126_19130805\oocihm.N_00126_19130805.4.txt</t>
         </is>
       </c>
       <c r="R213" s="1" t="n">
@@ -22066,7 +22066,7 @@
       </c>
       <c r="X213" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.4.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.4.txt</t>
         </is>
       </c>
       <c r="Y213" s="1" t="n">
@@ -22146,14 +22146,14 @@
       </c>
       <c r="Q214" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00126_19130805\oocihm.N_00126_19130805.5.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00126_19130805\oocihm.N_00126_19130805.5.txt</t>
         </is>
       </c>
       <c r="R214" s="1" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="S214" s="1" t="n">
-        <v>-69</v>
+        <v>-70</v>
       </c>
       <c r="T214" s="1" t="n">
         <v>554</v>
@@ -22173,7 +22173,7 @@
       </c>
       <c r="X214" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.5.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.5.txt</t>
         </is>
       </c>
       <c r="Y214" s="1" t="n">
@@ -22253,7 +22253,7 @@
       </c>
       <c r="Q215" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00126_19130805\oocihm.N_00126_19130805.6.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00126_19130805\oocihm.N_00126_19130805.6.txt</t>
         </is>
       </c>
       <c r="R215" s="1" t="n">
@@ -22280,7 +22280,7 @@
       </c>
       <c r="X215" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.6.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.6.txt</t>
         </is>
       </c>
       <c r="Y215" s="1" t="n">
@@ -22360,7 +22360,7 @@
       </c>
       <c r="Q216" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00126_19130805\oocihm.N_00126_19130805.7.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00126_19130805\oocihm.N_00126_19130805.7.txt</t>
         </is>
       </c>
       <c r="R216" s="1" t="n">
@@ -22387,7 +22387,7 @@
       </c>
       <c r="X216" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.7.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.7.txt</t>
         </is>
       </c>
       <c r="Y216" s="1" t="n">
@@ -22467,7 +22467,7 @@
       </c>
       <c r="Q217" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00126_19130805\oocihm.N_00126_19130805.8.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00126_19130805\oocihm.N_00126_19130805.8.txt</t>
         </is>
       </c>
       <c r="R217" s="1" t="n">
@@ -22494,7 +22494,7 @@
       </c>
       <c r="X217" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.8.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.8.txt</t>
         </is>
       </c>
       <c r="Y217" s="1" t="n">
@@ -22574,7 +22574,7 @@
       </c>
       <c r="Q218" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00138_18940629\oocihm.N_00138_18940629.1.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00138_18940629\oocihm.N_00138_18940629.1.txt</t>
         </is>
       </c>
       <c r="R218" s="1" t="n">
@@ -22601,7 +22601,7 @@
       </c>
       <c r="X218" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.1.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.1.txt</t>
         </is>
       </c>
       <c r="Y218" s="1" t="n">
@@ -22681,7 +22681,7 @@
       </c>
       <c r="Q219" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00138_18940629\oocihm.N_00138_18940629.2.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00138_18940629\oocihm.N_00138_18940629.2.txt</t>
         </is>
       </c>
       <c r="R219" s="1" t="n">
@@ -22708,7 +22708,7 @@
       </c>
       <c r="X219" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.2.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.2.txt</t>
         </is>
       </c>
       <c r="Y219" s="1" t="n">
@@ -22788,14 +22788,14 @@
       </c>
       <c r="Q220" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00138_18940629\oocihm.N_00138_18940629.3.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00138_18940629\oocihm.N_00138_18940629.3.txt</t>
         </is>
       </c>
       <c r="R220" s="1" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="S220" s="1" t="n">
-        <v>-116</v>
+        <v>-120</v>
       </c>
       <c r="T220" s="1" t="n">
         <v>892</v>
@@ -22815,7 +22815,7 @@
       </c>
       <c r="X220" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.3.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.3.txt</t>
         </is>
       </c>
       <c r="Y220" s="1" t="n">
@@ -22895,7 +22895,7 @@
       </c>
       <c r="Q221" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00138_18940629\oocihm.N_00138_18940629.4.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00138_18940629\oocihm.N_00138_18940629.4.txt</t>
         </is>
       </c>
       <c r="R221" s="1" t="n">
@@ -22922,7 +22922,7 @@
       </c>
       <c r="X221" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.4.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.4.txt</t>
         </is>
       </c>
       <c r="Y221" s="1" t="n">
@@ -23002,7 +23002,7 @@
       </c>
       <c r="Q222" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00138_18940629\oocihm.N_00138_18940629.5.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00138_18940629\oocihm.N_00138_18940629.5.txt</t>
         </is>
       </c>
       <c r="R222" s="1" t="n">
@@ -23029,7 +23029,7 @@
       </c>
       <c r="X222" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.5.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.5.txt</t>
         </is>
       </c>
       <c r="Y222" s="1" t="n">
@@ -23109,7 +23109,7 @@
       </c>
       <c r="Q223" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00138_18940629\oocihm.N_00138_18940629.6.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00138_18940629\oocihm.N_00138_18940629.6.txt</t>
         </is>
       </c>
       <c r="R223" s="1" t="n">
@@ -23136,7 +23136,7 @@
       </c>
       <c r="X223" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.6.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.6.txt</t>
         </is>
       </c>
       <c r="Y223" s="1" t="n">
@@ -23216,7 +23216,7 @@
       </c>
       <c r="Q224" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00138_18940629\oocihm.N_00138_18940629.7.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00138_18940629\oocihm.N_00138_18940629.7.txt</t>
         </is>
       </c>
       <c r="R224" s="1" t="n">
@@ -23243,7 +23243,7 @@
       </c>
       <c r="X224" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.7.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.7.txt</t>
         </is>
       </c>
       <c r="Y224" s="1" t="n">
@@ -23323,7 +23323,7 @@
       </c>
       <c r="Q225" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00138_18940629\oocihm.N_00138_18940629.8.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00138_18940629\oocihm.N_00138_18940629.8.txt</t>
         </is>
       </c>
       <c r="R225" s="1" t="n">
@@ -23350,7 +23350,7 @@
       </c>
       <c r="X225" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.8.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.8.txt</t>
         </is>
       </c>
       <c r="Y225" s="1" t="n">
@@ -23430,7 +23430,7 @@
       </c>
       <c r="Q226" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18750610\oocihm.N_00155_18750610.1.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18750610\oocihm.N_00155_18750610.1.txt</t>
         </is>
       </c>
       <c r="R226" s="1" t="n">
@@ -23457,7 +23457,7 @@
       </c>
       <c r="X226" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00155_18750610\oocihm.N_00155_18750610.1.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00155_18750610\oocihm.N_00155_18750610.1.txt</t>
         </is>
       </c>
       <c r="Y226" s="1" t="n">
@@ -23537,7 +23537,7 @@
       </c>
       <c r="Q227" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18750610\oocihm.N_00155_18750610.2.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18750610\oocihm.N_00155_18750610.2.txt</t>
         </is>
       </c>
       <c r="R227" s="1" t="n">
@@ -23564,7 +23564,7 @@
       </c>
       <c r="X227" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00155_18750610\oocihm.N_00155_18750610.2.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00155_18750610\oocihm.N_00155_18750610.2.txt</t>
         </is>
       </c>
       <c r="Y227" s="1" t="n">
@@ -23644,14 +23644,14 @@
       </c>
       <c r="Q228" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18750610\oocihm.N_00155_18750610.3.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18750610\oocihm.N_00155_18750610.3.txt</t>
         </is>
       </c>
       <c r="R228" s="1" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="S228" s="1" t="n">
-        <v>-262</v>
+        <v>-264</v>
       </c>
       <c r="T228" s="1" t="n">
         <v>972</v>
@@ -23671,7 +23671,7 @@
       </c>
       <c r="X228" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00155_18750610\oocihm.N_00155_18750610.3.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00155_18750610\oocihm.N_00155_18750610.3.txt</t>
         </is>
       </c>
       <c r="Y228" s="1" t="n">
@@ -23751,7 +23751,7 @@
       </c>
       <c r="Q229" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18750610\oocihm.N_00155_18750610.4.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18750610\oocihm.N_00155_18750610.4.txt</t>
         </is>
       </c>
       <c r="R229" s="1" t="n">
@@ -23778,7 +23778,7 @@
       </c>
       <c r="X229" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00155_18750610\oocihm.N_00155_18750610.4.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00155_18750610\oocihm.N_00155_18750610.4.txt</t>
         </is>
       </c>
       <c r="Y229" s="1" t="n">
@@ -23858,7 +23858,7 @@
       </c>
       <c r="Q230" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18880712\oocihm.N_00155_18880712.1.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18880712\oocihm.N_00155_18880712.1.txt</t>
         </is>
       </c>
       <c r="R230" s="1" t="n">
@@ -23885,7 +23885,7 @@
       </c>
       <c r="X230" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00155_18880712\oocihm.N_00155_18880712.1.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00155_18880712\oocihm.N_00155_18880712.1.txt</t>
         </is>
       </c>
       <c r="Y230" s="1" t="n">
@@ -23965,7 +23965,7 @@
       </c>
       <c r="Q231" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18880712\oocihm.N_00155_18880712.2.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18880712\oocihm.N_00155_18880712.2.txt</t>
         </is>
       </c>
       <c r="R231" s="1" t="n">
@@ -23992,7 +23992,7 @@
       </c>
       <c r="X231" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00155_18880712\oocihm.N_00155_18880712.2.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00155_18880712\oocihm.N_00155_18880712.2.txt</t>
         </is>
       </c>
       <c r="Y231" s="1" t="n">
@@ -24072,7 +24072,7 @@
       </c>
       <c r="Q232" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18880712\oocihm.N_00155_18880712.3.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18880712\oocihm.N_00155_18880712.3.txt</t>
         </is>
       </c>
       <c r="R232" s="1" t="n">
@@ -24099,7 +24099,7 @@
       </c>
       <c r="X232" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00155_18880712\oocihm.N_00155_18880712.3.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00155_18880712\oocihm.N_00155_18880712.3.txt</t>
         </is>
       </c>
       <c r="Y232" s="1" t="n">
@@ -24179,7 +24179,7 @@
       </c>
       <c r="Q233" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18880712\oocihm.N_00155_18880712.4.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18880712\oocihm.N_00155_18880712.4.txt</t>
         </is>
       </c>
       <c r="R233" s="1" t="n">
@@ -24206,7 +24206,7 @@
       </c>
       <c r="X233" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00155_18880712\oocihm.N_00155_18880712.4.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00155_18880712\oocihm.N_00155_18880712.4.txt</t>
         </is>
       </c>
       <c r="Y233" s="1" t="n">
@@ -24286,7 +24286,7 @@
       </c>
       <c r="Q234" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18880712\oocihm.N_00155_18880712.5.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18880712\oocihm.N_00155_18880712.5.txt</t>
         </is>
       </c>
       <c r="R234" s="1" t="n">
@@ -24313,7 +24313,7 @@
       </c>
       <c r="X234" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00155_18880712\oocihm.N_00155_18880712.5.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00155_18880712\oocihm.N_00155_18880712.5.txt</t>
         </is>
       </c>
       <c r="Y234" s="1" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="Q235" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18880712\oocihm.N_00155_18880712.6.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18880712\oocihm.N_00155_18880712.6.txt</t>
         </is>
       </c>
       <c r="R235" s="1" t="n">
@@ -24420,7 +24420,7 @@
       </c>
       <c r="X235" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00155_18880712\oocihm.N_00155_18880712.6.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00155_18880712\oocihm.N_00155_18880712.6.txt</t>
         </is>
       </c>
       <c r="Y235" s="1" t="n">
@@ -24500,7 +24500,7 @@
       </c>
       <c r="Q236" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18880712\oocihm.N_00155_18880712.7.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18880712\oocihm.N_00155_18880712.7.txt</t>
         </is>
       </c>
       <c r="R236" s="1" t="n">
@@ -24527,7 +24527,7 @@
       </c>
       <c r="X236" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00155_18880712\oocihm.N_00155_18880712.7.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00155_18880712\oocihm.N_00155_18880712.7.txt</t>
         </is>
       </c>
       <c r="Y236" s="1" t="n">
@@ -24607,7 +24607,7 @@
       </c>
       <c r="Q237" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18880712\oocihm.N_00155_18880712.8.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18880712\oocihm.N_00155_18880712.8.txt</t>
         </is>
       </c>
       <c r="R237" s="1" t="n">
@@ -24634,7 +24634,7 @@
       </c>
       <c r="X237" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00155_18880712\oocihm.N_00155_18880712.8.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00155_18880712\oocihm.N_00155_18880712.8.txt</t>
         </is>
       </c>
       <c r="Y237" s="1" t="n">
@@ -24714,7 +24714,7 @@
       </c>
       <c r="Q238" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00219_18600707\oocihm.N_00219_18600707.1.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00219_18600707\oocihm.N_00219_18600707.1.txt</t>
         </is>
       </c>
       <c r="R238" s="1" t="n">
@@ -24741,7 +24741,7 @@
       </c>
       <c r="X238" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00219_18600707\oocihm.N_00219_18600707.1.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00219_18600707\oocihm.N_00219_18600707.1.txt</t>
         </is>
       </c>
       <c r="Y238" s="1" t="n">
@@ -24821,7 +24821,7 @@
       </c>
       <c r="Q239" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00219_18600707\oocihm.N_00219_18600707.2.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00219_18600707\oocihm.N_00219_18600707.2.txt</t>
         </is>
       </c>
       <c r="R239" s="1" t="n">
@@ -24848,7 +24848,7 @@
       </c>
       <c r="X239" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00219_18600707\oocihm.N_00219_18600707.2.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00219_18600707\oocihm.N_00219_18600707.2.txt</t>
         </is>
       </c>
       <c r="Y239" s="1" t="n">
@@ -24928,7 +24928,7 @@
       </c>
       <c r="Q240" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00219_18600707\oocihm.N_00219_18600707.3.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00219_18600707\oocihm.N_00219_18600707.3.txt</t>
         </is>
       </c>
       <c r="R240" s="1" t="n">
@@ -24955,7 +24955,7 @@
       </c>
       <c r="X240" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00219_18600707\oocihm.N_00219_18600707.3.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00219_18600707\oocihm.N_00219_18600707.3.txt</t>
         </is>
       </c>
       <c r="Y240" s="1" t="n">
@@ -25035,7 +25035,7 @@
       </c>
       <c r="Q241" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00219_18600707\oocihm.N_00219_18600707.4.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00219_18600707\oocihm.N_00219_18600707.4.txt</t>
         </is>
       </c>
       <c r="R241" s="1" t="n">
@@ -25062,7 +25062,7 @@
       </c>
       <c r="X241" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00219_18600707\oocihm.N_00219_18600707.4.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00219_18600707\oocihm.N_00219_18600707.4.txt</t>
         </is>
       </c>
       <c r="Y241" s="1" t="n">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/paddle_variants_abbyy_artifacts.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/paddle_variants_abbyy_artifacts.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Overall Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overall Summary" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Overall Summary'!$A$1:$AA$241</definedName>
@@ -676,10 +676,10 @@
         <v>10614</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>7847</v>
+        <v>5844</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>11041</v>
+        <v>6813</v>
       </c>
       <c r="F6" s="1" t="n"/>
       <c r="G6" s="1" t="n"/>
@@ -793,13 +793,13 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E9" s="1" t="inlineStr"/>
       <c r="F9" s="1" t="n"/>
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E10" s="1" t="inlineStr"/>
       <c r="F10" s="1" t="n"/>
@@ -871,16 +871,16 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F11" s="1" t="n"/>
       <c r="G11" s="1" t="n"/>
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="M15" s="1" t="n">
-        <v>2665</v>
+        <v>1128</v>
       </c>
       <c r="N15" s="1" t="n">
         <v>5886</v>
@@ -1143,7 +1143,7 @@
         </is>
       </c>
       <c r="R15" s="1" t="n">
-        <v>4114</v>
+        <v>2131</v>
       </c>
       <c r="S15" s="1" t="n">
         <v>5908</v>
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="M16" s="1" t="n">
-        <v>2559</v>
+        <v>2282</v>
       </c>
       <c r="N16" s="1" t="n">
         <v>20186</v>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="R16" s="1" t="n">
-        <v>1926</v>
+        <v>1756</v>
       </c>
       <c r="S16" s="1" t="n">
         <v>13894</v>
@@ -1290,7 +1290,7 @@
         </is>
       </c>
       <c r="M17" s="1" t="n">
-        <v>547</v>
+        <v>513</v>
       </c>
       <c r="N17" s="1" t="n">
         <v>5493</v>
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="R17" s="1" t="n">
-        <v>898</v>
+        <v>662</v>
       </c>
       <c r="S17" s="1" t="n">
         <v>5211</v>
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="M18" s="1" t="n">
-        <v>803</v>
+        <v>761</v>
       </c>
       <c r="N18" s="1" t="n">
         <v>7274</v>
@@ -1392,7 +1392,7 @@
         </is>
       </c>
       <c r="R18" s="1" t="n">
-        <v>1384</v>
+        <v>749</v>
       </c>
       <c r="S18" s="1" t="n">
         <v>7206</v>
@@ -1456,7 +1456,7 @@
         </is>
       </c>
       <c r="M19" s="1" t="n">
-        <v>196</v>
+        <v>146</v>
       </c>
       <c r="N19" s="1" t="n">
         <v>3943</v>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="R19" s="1" t="n">
-        <v>920</v>
+        <v>354</v>
       </c>
       <c r="S19" s="1" t="n">
         <v>8420</v>
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="M20" s="1" t="n">
-        <v>263</v>
+        <v>232</v>
       </c>
       <c r="N20" s="1" t="n">
         <v>7509</v>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="R20" s="1" t="n">
-        <v>863</v>
+        <v>424</v>
       </c>
       <c r="S20" s="1" t="n">
         <v>5610</v>
@@ -1622,7 +1622,7 @@
         </is>
       </c>
       <c r="M21" s="1" t="n">
-        <v>814</v>
+        <v>782</v>
       </c>
       <c r="N21" s="1" t="n">
         <v>5430</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="R21" s="1" t="n">
-        <v>936</v>
+        <v>737</v>
       </c>
       <c r="S21" s="1" t="n">
         <v>3526</v>
@@ -1876,7 +1876,7 @@
         <v>362</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>31</v>
+        <v>313</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>765</v>
@@ -1903,7 +1903,7 @@
         <v>349</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>18</v>
+        <v>300</v>
       </c>
       <c r="M25" s="1" t="n">
         <v>685</v>
@@ -1927,10 +1927,10 @@
         </is>
       </c>
       <c r="R25" s="1" t="n">
-        <v>266</v>
+        <v>51</v>
       </c>
       <c r="S25" s="1" t="n">
-        <v>-65</v>
+        <v>2</v>
       </c>
       <c r="T25" s="1" t="n">
         <v>602</v>
@@ -1954,7 +1954,7 @@
         </is>
       </c>
       <c r="Y25" s="1" t="n">
-        <v>331</v>
+        <v>49</v>
       </c>
       <c r="Z25" s="1" t="n">
         <v>546</v>
@@ -1983,7 +1983,7 @@
         <v>344</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>-19</v>
+        <v>306</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>864</v>
@@ -2010,7 +2010,7 @@
         <v>345</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>-18</v>
+        <v>307</v>
       </c>
       <c r="M26" s="1" t="n">
         <v>783</v>
@@ -2034,10 +2034,10 @@
         </is>
       </c>
       <c r="R26" s="1" t="n">
-        <v>275</v>
+        <v>53</v>
       </c>
       <c r="S26" s="1" t="n">
-        <v>-88</v>
+        <v>15</v>
       </c>
       <c r="T26" s="1" t="n">
         <v>723</v>
@@ -2061,7 +2061,7 @@
         </is>
       </c>
       <c r="Y26" s="1" t="n">
-        <v>363</v>
+        <v>38</v>
       </c>
       <c r="Z26" s="1" t="n">
         <v>633</v>
@@ -2090,7 +2090,7 @@
         <v>456</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>41</v>
+        <v>360</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>944</v>
@@ -2117,7 +2117,7 @@
         <v>450</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>35</v>
+        <v>354</v>
       </c>
       <c r="M27" s="1" t="n">
         <v>877</v>
@@ -2141,10 +2141,10 @@
         </is>
       </c>
       <c r="R27" s="1" t="n">
-        <v>403</v>
+        <v>162</v>
       </c>
       <c r="S27" s="1" t="n">
-        <v>-12</v>
+        <v>66</v>
       </c>
       <c r="T27" s="1" t="n">
         <v>821</v>
@@ -2168,7 +2168,7 @@
         </is>
       </c>
       <c r="Y27" s="1" t="n">
-        <v>415</v>
+        <v>96</v>
       </c>
       <c r="Z27" s="1" t="n">
         <v>702</v>
@@ -2197,7 +2197,7 @@
         <v>437</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>56</v>
+        <v>342</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>1058</v>
@@ -2224,7 +2224,7 @@
         <v>428</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>47</v>
+        <v>333</v>
       </c>
       <c r="M28" s="1" t="n">
         <v>934</v>
@@ -2248,10 +2248,10 @@
         </is>
       </c>
       <c r="R28" s="1" t="n">
-        <v>354</v>
+        <v>167</v>
       </c>
       <c r="S28" s="1" t="n">
-        <v>-27</v>
+        <v>72</v>
       </c>
       <c r="T28" s="1" t="n">
         <v>874</v>
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="Y28" s="1" t="n">
-        <v>381</v>
+        <v>95</v>
       </c>
       <c r="Z28" s="1" t="n">
         <v>736</v>
@@ -2304,7 +2304,7 @@
         <v>248</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>-45</v>
+        <v>188</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>830</v>
@@ -2331,7 +2331,7 @@
         <v>236</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>-57</v>
+        <v>176</v>
       </c>
       <c r="M29" s="1" t="n">
         <v>737</v>
@@ -2355,10 +2355,10 @@
         </is>
       </c>
       <c r="R29" s="1" t="n">
-        <v>216</v>
+        <v>35</v>
       </c>
       <c r="S29" s="1" t="n">
-        <v>-77</v>
+        <v>-25</v>
       </c>
       <c r="T29" s="1" t="n">
         <v>707</v>
@@ -2382,7 +2382,7 @@
         </is>
       </c>
       <c r="Y29" s="1" t="n">
-        <v>293</v>
+        <v>60</v>
       </c>
       <c r="Z29" s="1" t="n">
         <v>499</v>
@@ -2411,7 +2411,7 @@
         <v>1100</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>76</v>
+        <v>144</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>1809</v>
@@ -2438,7 +2438,7 @@
         <v>1101</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>77</v>
+        <v>145</v>
       </c>
       <c r="M30" s="1" t="n">
         <v>1685</v>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="R30" s="1" t="n">
-        <v>493</v>
+        <v>369</v>
       </c>
       <c r="S30" s="1" t="n">
-        <v>-531</v>
+        <v>-587</v>
       </c>
       <c r="T30" s="1" t="n">
         <v>802</v>
@@ -2489,7 +2489,7 @@
         </is>
       </c>
       <c r="Y30" s="1" t="n">
-        <v>1024</v>
+        <v>956</v>
       </c>
       <c r="Z30" s="1" t="n">
         <v>1083</v>
@@ -2518,7 +2518,7 @@
         <v>912</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>-121</v>
+        <v>110</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>1553</v>
@@ -2545,7 +2545,7 @@
         <v>895</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>-138</v>
+        <v>93</v>
       </c>
       <c r="M31" s="1" t="n">
         <v>1486</v>
@@ -2569,10 +2569,10 @@
         </is>
       </c>
       <c r="R31" s="1" t="n">
-        <v>462</v>
+        <v>268</v>
       </c>
       <c r="S31" s="1" t="n">
-        <v>-571</v>
+        <v>-534</v>
       </c>
       <c r="T31" s="1" t="n">
         <v>788</v>
@@ -2596,7 +2596,7 @@
         </is>
       </c>
       <c r="Y31" s="1" t="n">
-        <v>1033</v>
+        <v>802</v>
       </c>
       <c r="Z31" s="1" t="n">
         <v>1199</v>
@@ -2625,7 +2625,7 @@
         <v>244</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>-30</v>
+        <v>209</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>744</v>
@@ -2652,7 +2652,7 @@
         <v>218</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>-56</v>
+        <v>183</v>
       </c>
       <c r="M32" s="1" t="n">
         <v>604</v>
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="R32" s="1" t="n">
-        <v>196</v>
+        <v>23</v>
       </c>
       <c r="S32" s="1" t="n">
-        <v>-78</v>
+        <v>-12</v>
       </c>
       <c r="T32" s="1" t="n">
         <v>569</v>
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="Y32" s="1" t="n">
-        <v>274</v>
+        <v>35</v>
       </c>
       <c r="Z32" s="1" t="n">
         <v>510</v>
@@ -2732,7 +2732,7 @@
         <v>29</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>44</v>
@@ -2759,7 +2759,7 @@
         <v>24</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M33" s="1" t="n">
         <v>35</v>
@@ -2786,7 +2786,7 @@
         <v>24</v>
       </c>
       <c r="S33" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T33" s="1" t="n">
         <v>34</v>
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="Y33" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z33" s="1" t="n">
         <v>18</v>
@@ -2839,7 +2839,7 @@
         <v>8</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>74</v>
@@ -2866,7 +2866,7 @@
         <v>4</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="M34" s="1" t="n">
         <v>39</v>
@@ -2890,10 +2890,10 @@
         </is>
       </c>
       <c r="R34" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S34" s="1" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="T34" s="1" t="n">
         <v>38</v>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="Y34" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Z34" s="1" t="n">
         <v>68</v>
@@ -2946,7 +2946,7 @@
         <v>5</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>139</v>
@@ -2973,7 +2973,7 @@
         <v>3</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="M35" s="1" t="n">
         <v>95</v>
@@ -3000,7 +3000,7 @@
         <v>4</v>
       </c>
       <c r="S35" s="1" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T35" s="1" t="n">
         <v>130</v>
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="Y35" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z35" s="1" t="n">
         <v>90</v>
@@ -3053,7 +3053,7 @@
         <v>6</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>149</v>
@@ -3080,7 +3080,7 @@
         <v>5</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M36" s="1" t="n">
         <v>102</v>
@@ -3107,7 +3107,7 @@
         <v>6</v>
       </c>
       <c r="S36" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T36" s="1" t="n">
         <v>154</v>
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="Y36" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z36" s="1" t="n">
         <v>94</v>
@@ -3160,7 +3160,7 @@
         <v>4</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F37" s="1" t="n">
         <v>152</v>
@@ -3187,7 +3187,7 @@
         <v>3</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="M37" s="1" t="n">
         <v>112</v>
@@ -3211,10 +3211,10 @@
         </is>
       </c>
       <c r="R37" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S37" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T37" s="1" t="n">
         <v>158</v>
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="Y37" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z37" s="1" t="n">
         <v>95</v>
@@ -3267,7 +3267,7 @@
         <v>6</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F38" s="1" t="n">
         <v>156</v>
@@ -3294,7 +3294,7 @@
         <v>6</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M38" s="1" t="n">
         <v>114</v>
@@ -3321,7 +3321,7 @@
         <v>5</v>
       </c>
       <c r="S38" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T38" s="1" t="n">
         <v>176</v>
@@ -3345,7 +3345,7 @@
         </is>
       </c>
       <c r="Y38" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z38" s="1" t="n">
         <v>99</v>
@@ -3374,7 +3374,7 @@
         <v>16</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F39" s="1" t="n">
         <v>175</v>
@@ -3401,7 +3401,7 @@
         <v>12</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M39" s="1" t="n">
         <v>131</v>
@@ -3428,7 +3428,7 @@
         <v>12</v>
       </c>
       <c r="S39" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T39" s="1" t="n">
         <v>174</v>
@@ -3452,7 +3452,7 @@
         </is>
       </c>
       <c r="Y39" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z39" s="1" t="n">
         <v>93</v>
@@ -3532,10 +3532,10 @@
         </is>
       </c>
       <c r="R40" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S40" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T40" s="1" t="n">
         <v>234</v>
@@ -3588,7 +3588,7 @@
         <v>14</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F41" s="1" t="n">
         <v>168</v>
@@ -3615,7 +3615,7 @@
         <v>8</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" s="1" t="n">
         <v>121</v>
@@ -3642,7 +3642,7 @@
         <v>11</v>
       </c>
       <c r="S41" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T41" s="1" t="n">
         <v>162</v>
@@ -3666,7 +3666,7 @@
         </is>
       </c>
       <c r="Y41" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z41" s="1" t="n">
         <v>94</v>
@@ -3695,7 +3695,7 @@
         <v>7</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F42" s="1" t="n">
         <v>160</v>
@@ -3722,7 +3722,7 @@
         <v>7</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M42" s="1" t="n">
         <v>115</v>
@@ -3746,10 +3746,10 @@
         </is>
       </c>
       <c r="R42" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="S42" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T42" s="1" t="n">
         <v>187</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y42" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z42" s="1" t="n">
         <v>97</v>
@@ -3802,7 +3802,7 @@
         <v>9</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F43" s="1" t="n">
         <v>160</v>
@@ -3829,7 +3829,7 @@
         <v>10</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M43" s="1" t="n">
         <v>117</v>
@@ -3856,7 +3856,7 @@
         <v>8</v>
       </c>
       <c r="S43" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T43" s="1" t="n">
         <v>160</v>
@@ -3880,7 +3880,7 @@
         </is>
       </c>
       <c r="Y43" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z43" s="1" t="n">
         <v>98</v>
@@ -3960,10 +3960,10 @@
         </is>
       </c>
       <c r="R44" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S44" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T44" s="1" t="n">
         <v>176</v>
@@ -4016,7 +4016,7 @@
         <v>14</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F45" s="1" t="n">
         <v>106</v>
@@ -4043,7 +4043,7 @@
         <v>13</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M45" s="1" t="n">
         <v>75</v>
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="R45" s="1" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="S45" s="1" t="n">
         <v>22</v>
@@ -4094,7 +4094,7 @@
         </is>
       </c>
       <c r="Y45" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z45" s="1" t="n">
         <v>72</v>
@@ -4123,7 +4123,7 @@
         <v>11</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>-7</v>
+        <v>1</v>
       </c>
       <c r="F46" s="1" t="n">
         <v>120</v>
@@ -4150,7 +4150,7 @@
         <v>5</v>
       </c>
       <c r="L46" s="1" t="n">
-        <v>-13</v>
+        <v>-5</v>
       </c>
       <c r="M46" s="1" t="n">
         <v>81</v>
@@ -4174,10 +4174,10 @@
         </is>
       </c>
       <c r="R46" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S46" s="1" t="n">
-        <v>-13</v>
+        <v>-6</v>
       </c>
       <c r="T46" s="1" t="n">
         <v>80</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y46" s="1" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="Z46" s="1" t="n">
         <v>86</v>
@@ -4230,7 +4230,7 @@
         <v>3</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="F47" s="1" t="n">
         <v>111</v>
@@ -4257,7 +4257,7 @@
         <v>3</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="M47" s="1" t="n">
         <v>76</v>
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="R47" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S47" s="1" t="n">
         <v>-1</v>
@@ -4308,7 +4308,7 @@
         </is>
       </c>
       <c r="Y47" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z47" s="1" t="n">
         <v>78</v>
@@ -4444,7 +4444,7 @@
         <v>9</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" s="1" t="n">
         <v>138</v>
@@ -4471,7 +4471,7 @@
         <v>11</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M49" s="1" t="n">
         <v>102</v>
@@ -4495,7 +4495,7 @@
         </is>
       </c>
       <c r="R49" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="S49" s="1" t="n">
         <v>6</v>
@@ -4522,7 +4522,7 @@
         </is>
       </c>
       <c r="Y49" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z49" s="1" t="n">
         <v>97</v>
@@ -4658,7 +4658,7 @@
         <v>11</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F51" s="1" t="n">
         <v>162</v>
@@ -4685,7 +4685,7 @@
         <v>6</v>
       </c>
       <c r="L51" s="1" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M51" s="1" t="n">
         <v>118</v>
@@ -4712,7 +4712,7 @@
         <v>11</v>
       </c>
       <c r="S51" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T51" s="1" t="n">
         <v>188</v>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="Y51" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z51" s="1" t="n">
         <v>99</v>
@@ -4765,7 +4765,7 @@
         <v>8</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="F52" s="1" t="n">
         <v>162</v>
@@ -4792,7 +4792,7 @@
         <v>8</v>
       </c>
       <c r="L52" s="1" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="M52" s="1" t="n">
         <v>118</v>
@@ -4819,7 +4819,7 @@
         <v>7</v>
       </c>
       <c r="S52" s="1" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="T52" s="1" t="n">
         <v>154</v>
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="Y52" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z52" s="1" t="n">
         <v>96</v>
@@ -4872,7 +4872,7 @@
         <v>9</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F53" s="1" t="n">
         <v>155</v>
@@ -4899,7 +4899,7 @@
         <v>8</v>
       </c>
       <c r="L53" s="1" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M53" s="1" t="n">
         <v>112</v>
@@ -4926,7 +4926,7 @@
         <v>16</v>
       </c>
       <c r="S53" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T53" s="1" t="n">
         <v>178</v>
@@ -4950,7 +4950,7 @@
         </is>
       </c>
       <c r="Y53" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z53" s="1" t="n">
         <v>96</v>
@@ -4979,7 +4979,7 @@
         <v>13</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54" s="1" t="n">
         <v>164</v>
@@ -5006,7 +5006,7 @@
         <v>11</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="M54" s="1" t="n">
         <v>120</v>
@@ -5030,7 +5030,7 @@
         </is>
       </c>
       <c r="R54" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="S54" s="1" t="n">
         <v>1</v>
@@ -5057,7 +5057,7 @@
         </is>
       </c>
       <c r="Y54" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z54" s="1" t="n">
         <v>100</v>
@@ -5086,7 +5086,7 @@
         <v>10</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F55" s="1" t="n">
         <v>177</v>
@@ -5113,7 +5113,7 @@
         <v>9</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M55" s="1" t="n">
         <v>133</v>
@@ -5140,7 +5140,7 @@
         <v>14</v>
       </c>
       <c r="S55" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T55" s="1" t="n">
         <v>215</v>
@@ -5164,7 +5164,7 @@
         </is>
       </c>
       <c r="Y55" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z55" s="1" t="n">
         <v>96</v>
@@ -5244,10 +5244,10 @@
         </is>
       </c>
       <c r="R56" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S56" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T56" s="1" t="n">
         <v>66</v>
@@ -5621,7 +5621,7 @@
         <v>8</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F60" s="1" t="n">
         <v>115</v>
@@ -5648,7 +5648,7 @@
         <v>7</v>
       </c>
       <c r="L60" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M60" s="1" t="n">
         <v>78</v>
@@ -5675,7 +5675,7 @@
         <v>12</v>
       </c>
       <c r="S60" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T60" s="1" t="n">
         <v>144</v>
@@ -5699,7 +5699,7 @@
         </is>
       </c>
       <c r="Y60" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z60" s="1" t="n">
         <v>51</v>
@@ -5728,7 +5728,7 @@
         <v>3</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="F61" s="1" t="n">
         <v>46</v>
@@ -5755,7 +5755,7 @@
         <v>2</v>
       </c>
       <c r="L61" s="1" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="M61" s="1" t="n">
         <v>43</v>
@@ -5782,7 +5782,7 @@
         <v>1</v>
       </c>
       <c r="S61" s="1" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="T61" s="1" t="n">
         <v>42</v>
@@ -5806,7 +5806,7 @@
         </is>
       </c>
       <c r="Y61" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z61" s="1" t="n">
         <v>48</v>
@@ -5835,7 +5835,7 @@
         <v>4</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F62" s="1" t="n">
         <v>108</v>
@@ -5862,7 +5862,7 @@
         <v>2</v>
       </c>
       <c r="L62" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" s="1" t="n">
         <v>78</v>
@@ -5886,10 +5886,10 @@
         </is>
       </c>
       <c r="R62" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="S62" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T62" s="1" t="n">
         <v>117</v>
@@ -5913,7 +5913,7 @@
         </is>
       </c>
       <c r="Y62" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z62" s="1" t="n">
         <v>70</v>
@@ -5942,7 +5942,7 @@
         <v>10</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F63" s="1" t="n">
         <v>124</v>
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="L63" s="1" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="M63" s="1" t="n">
         <v>88</v>
@@ -5993,10 +5993,10 @@
         </is>
       </c>
       <c r="R63" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S63" s="1" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="T63" s="1" t="n">
         <v>114</v>
@@ -6020,7 +6020,7 @@
         </is>
       </c>
       <c r="Y63" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z63" s="1" t="n">
         <v>82</v>
@@ -6049,7 +6049,7 @@
         <v>8</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F64" s="1" t="n">
         <v>149</v>
@@ -6076,7 +6076,7 @@
         <v>7</v>
       </c>
       <c r="L64" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64" s="1" t="n">
         <v>107</v>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="R64" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="S64" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T64" s="1" t="n">
         <v>171</v>
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="Y64" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z64" s="1" t="n">
         <v>95</v>
@@ -6314,10 +6314,10 @@
         </is>
       </c>
       <c r="R66" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S66" s="1" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T66" s="1" t="n">
         <v>86</v>
@@ -6370,7 +6370,7 @@
         <v>13</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F67" s="1" t="n">
         <v>53</v>
@@ -6397,7 +6397,7 @@
         <v>14</v>
       </c>
       <c r="L67" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M67" s="1" t="n">
         <v>42</v>
@@ -6424,7 +6424,7 @@
         <v>15</v>
       </c>
       <c r="S67" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T67" s="1" t="n">
         <v>55</v>
@@ -6448,7 +6448,7 @@
         </is>
       </c>
       <c r="Y67" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z67" s="1" t="n">
         <v>38</v>
@@ -6584,7 +6584,7 @@
         <v>15</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="F69" s="1" t="n">
         <v>159</v>
@@ -6611,7 +6611,7 @@
         <v>15</v>
       </c>
       <c r="L69" s="1" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="M69" s="1" t="n">
         <v>115</v>
@@ -6635,7 +6635,7 @@
         </is>
       </c>
       <c r="R69" s="1" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="S69" s="1" t="n">
         <v>0</v>
@@ -6662,7 +6662,7 @@
         </is>
       </c>
       <c r="Y69" s="1" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="Z69" s="1" t="n">
         <v>95</v>
@@ -6691,7 +6691,7 @@
         <v>14</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="F70" s="1" t="n">
         <v>138</v>
@@ -6718,7 +6718,7 @@
         <v>10</v>
       </c>
       <c r="L70" s="1" t="n">
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="M70" s="1" t="n">
         <v>106</v>
@@ -6742,7 +6742,7 @@
         </is>
       </c>
       <c r="R70" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="S70" s="1" t="n">
         <v>-7</v>
@@ -6769,7 +6769,7 @@
         </is>
       </c>
       <c r="Y70" s="1" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="Z70" s="1" t="n">
         <v>89</v>
@@ -6798,7 +6798,7 @@
         <v>19</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F71" s="1" t="n">
         <v>163</v>
@@ -6825,7 +6825,7 @@
         <v>13</v>
       </c>
       <c r="L71" s="1" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="M71" s="1" t="n">
         <v>123</v>
@@ -6849,10 +6849,10 @@
         </is>
       </c>
       <c r="R71" s="1" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="S71" s="1" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="T71" s="1" t="n">
         <v>199</v>
@@ -6876,7 +6876,7 @@
         </is>
       </c>
       <c r="Y71" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Z71" s="1" t="n">
         <v>112</v>
@@ -6905,7 +6905,7 @@
         <v>12</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="F72" s="1" t="n">
         <v>144</v>
@@ -6932,7 +6932,7 @@
         <v>10</v>
       </c>
       <c r="L72" s="1" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="M72" s="1" t="n">
         <v>102</v>
@@ -6956,10 +6956,10 @@
         </is>
       </c>
       <c r="R72" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="S72" s="1" t="n">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="T72" s="1" t="n">
         <v>139</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y72" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Z72" s="1" t="n">
         <v>94</v>
@@ -7012,7 +7012,7 @@
         <v>13</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="F73" s="1" t="n">
         <v>144</v>
@@ -7039,7 +7039,7 @@
         <v>13</v>
       </c>
       <c r="L73" s="1" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="M73" s="1" t="n">
         <v>102</v>
@@ -7063,10 +7063,10 @@
         </is>
       </c>
       <c r="R73" s="1" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="S73" s="1" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
       <c r="T73" s="1" t="n">
         <v>157</v>
@@ -7090,7 +7090,7 @@
         </is>
       </c>
       <c r="Y73" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Z73" s="1" t="n">
         <v>92</v>
@@ -7119,7 +7119,7 @@
         <v>12</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="F74" s="1" t="n">
         <v>132</v>
@@ -7146,7 +7146,7 @@
         <v>8</v>
       </c>
       <c r="L74" s="1" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="M74" s="1" t="n">
         <v>93</v>
@@ -7170,10 +7170,10 @@
         </is>
       </c>
       <c r="R74" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="S74" s="1" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="T74" s="1" t="n">
         <v>132</v>
@@ -7197,7 +7197,7 @@
         </is>
       </c>
       <c r="Y74" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z74" s="1" t="n">
         <v>94</v>
@@ -7277,10 +7277,10 @@
         </is>
       </c>
       <c r="R75" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="S75" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T75" s="1" t="n">
         <v>195</v>
@@ -7333,7 +7333,7 @@
         <v>20</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F76" s="1" t="n">
         <v>148</v>
@@ -7360,7 +7360,7 @@
         <v>12</v>
       </c>
       <c r="L76" s="1" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="M76" s="1" t="n">
         <v>110</v>
@@ -7384,10 +7384,10 @@
         </is>
       </c>
       <c r="R76" s="1" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="S76" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T76" s="1" t="n">
         <v>148</v>
@@ -7411,7 +7411,7 @@
         </is>
       </c>
       <c r="Y76" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Z76" s="1" t="n">
         <v>92</v>
@@ -7491,10 +7491,10 @@
         </is>
       </c>
       <c r="R77" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="S77" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T77" s="1" t="n">
         <v>182</v>
@@ -7547,7 +7547,7 @@
         <v>12</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F78" s="1" t="n">
         <v>81</v>
@@ -7574,7 +7574,7 @@
         <v>9</v>
       </c>
       <c r="L78" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M78" s="1" t="n">
         <v>61</v>
@@ -7598,10 +7598,10 @@
         </is>
       </c>
       <c r="R78" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S78" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T78" s="1" t="n">
         <v>67</v>
@@ -7625,7 +7625,7 @@
         </is>
       </c>
       <c r="Y78" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z78" s="1" t="n">
         <v>49</v>
@@ -7654,7 +7654,7 @@
         <v>16</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F79" s="1" t="n">
         <v>136</v>
@@ -7681,7 +7681,7 @@
         <v>13</v>
       </c>
       <c r="L79" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M79" s="1" t="n">
         <v>100</v>
@@ -7705,10 +7705,10 @@
         </is>
       </c>
       <c r="R79" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S79" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T79" s="1" t="n">
         <v>135</v>
@@ -7732,7 +7732,7 @@
         </is>
       </c>
       <c r="Y79" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z79" s="1" t="n">
         <v>88</v>
@@ -7761,7 +7761,7 @@
         <v>10</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="F80" s="1" t="n">
         <v>146</v>
@@ -7788,7 +7788,7 @@
         <v>11</v>
       </c>
       <c r="L80" s="1" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="M80" s="1" t="n">
         <v>111</v>
@@ -7812,10 +7812,10 @@
         </is>
       </c>
       <c r="R80" s="1" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="S80" s="1" t="n">
-        <v>6</v>
+        <v>-5</v>
       </c>
       <c r="T80" s="1" t="n">
         <v>171</v>
@@ -7839,7 +7839,7 @@
         </is>
       </c>
       <c r="Y80" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z80" s="1" t="n">
         <v>97</v>
@@ -7868,7 +7868,7 @@
         <v>12</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="F81" s="1" t="n">
         <v>140</v>
@@ -7895,7 +7895,7 @@
         <v>9</v>
       </c>
       <c r="L81" s="1" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="M81" s="1" t="n">
         <v>99</v>
@@ -7922,7 +7922,7 @@
         <v>6</v>
       </c>
       <c r="S81" s="1" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="T81" s="1" t="n">
         <v>95</v>
@@ -7946,7 +7946,7 @@
         </is>
       </c>
       <c r="Y81" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z81" s="1" t="n">
         <v>91</v>
@@ -7975,7 +7975,7 @@
         <v>14</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F82" s="1" t="n">
         <v>156</v>
@@ -8002,7 +8002,7 @@
         <v>14</v>
       </c>
       <c r="L82" s="1" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M82" s="1" t="n">
         <v>114</v>
@@ -8026,10 +8026,10 @@
         </is>
       </c>
       <c r="R82" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="S82" s="1" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="T82" s="1" t="n">
         <v>164</v>
@@ -8053,7 +8053,7 @@
         </is>
       </c>
       <c r="Y82" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Z82" s="1" t="n">
         <v>95</v>
@@ -8082,7 +8082,7 @@
         <v>14</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="F83" s="1" t="n">
         <v>148</v>
@@ -8109,7 +8109,7 @@
         <v>14</v>
       </c>
       <c r="L83" s="1" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="M83" s="1" t="n">
         <v>113</v>
@@ -8133,10 +8133,10 @@
         </is>
       </c>
       <c r="R83" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="S83" s="1" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="T83" s="1" t="n">
         <v>156</v>
@@ -8160,7 +8160,7 @@
         </is>
       </c>
       <c r="Y83" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z83" s="1" t="n">
         <v>96</v>
@@ -8240,10 +8240,10 @@
         </is>
       </c>
       <c r="R84" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S84" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T84" s="1" t="n">
         <v>143</v>
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="R85" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S85" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T85" s="1" t="n">
         <v>154</v>
@@ -8403,7 +8403,7 @@
         <v>5</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="F86" s="1" t="n">
         <v>139</v>
@@ -8430,7 +8430,7 @@
         <v>8</v>
       </c>
       <c r="L86" s="1" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="M86" s="1" t="n">
         <v>104</v>
@@ -8454,10 +8454,10 @@
         </is>
       </c>
       <c r="R86" s="1" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="S86" s="1" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="T86" s="1" t="n">
         <v>164</v>
@@ -8481,7 +8481,7 @@
         </is>
       </c>
       <c r="Y86" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Z86" s="1" t="n">
         <v>97</v>
@@ -8510,7 +8510,7 @@
         <v>6</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="F87" s="1" t="n">
         <v>134</v>
@@ -8537,7 +8537,7 @@
         <v>5</v>
       </c>
       <c r="L87" s="1" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="M87" s="1" t="n">
         <v>98</v>
@@ -8561,7 +8561,7 @@
         </is>
       </c>
       <c r="R87" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S87" s="1" t="n">
         <v>-2</v>
@@ -8588,7 +8588,7 @@
         </is>
       </c>
       <c r="Y87" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z87" s="1" t="n">
         <v>83</v>
@@ -8617,7 +8617,7 @@
         <v>9</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="F88" s="1" t="n">
         <v>147</v>
@@ -8644,7 +8644,7 @@
         <v>9</v>
       </c>
       <c r="L88" s="1" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="M88" s="1" t="n">
         <v>104</v>
@@ -8668,10 +8668,10 @@
         </is>
       </c>
       <c r="R88" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="S88" s="1" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="T88" s="1" t="n">
         <v>165</v>
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="Y88" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z88" s="1" t="n">
         <v>88</v>
@@ -8724,7 +8724,7 @@
         <v>8</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F89" s="1" t="n">
         <v>126</v>
@@ -8751,7 +8751,7 @@
         <v>7</v>
       </c>
       <c r="L89" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M89" s="1" t="n">
         <v>90</v>
@@ -8775,10 +8775,10 @@
         </is>
       </c>
       <c r="R89" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="S89" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T89" s="1" t="n">
         <v>141</v>
@@ -8802,7 +8802,7 @@
         </is>
       </c>
       <c r="Y89" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z89" s="1" t="n">
         <v>83</v>
@@ -8831,7 +8831,7 @@
         <v>5</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="F90" s="1" t="n">
         <v>129</v>
@@ -8858,7 +8858,7 @@
         <v>6</v>
       </c>
       <c r="L90" s="1" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="M90" s="1" t="n">
         <v>92</v>
@@ -8885,7 +8885,7 @@
         <v>4</v>
       </c>
       <c r="S90" s="1" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="T90" s="1" t="n">
         <v>129</v>
@@ -8909,7 +8909,7 @@
         </is>
       </c>
       <c r="Y90" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z90" s="1" t="n">
         <v>85</v>
@@ -8938,7 +8938,7 @@
         <v>8</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="F91" s="1" t="n">
         <v>133</v>
@@ -8965,7 +8965,7 @@
         <v>8</v>
       </c>
       <c r="L91" s="1" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="M91" s="1" t="n">
         <v>96</v>
@@ -8989,10 +8989,10 @@
         </is>
       </c>
       <c r="R91" s="1" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="S91" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T91" s="1" t="n">
         <v>151</v>
@@ -9016,7 +9016,7 @@
         </is>
       </c>
       <c r="Y91" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z91" s="1" t="n">
         <v>87</v>
@@ -9045,7 +9045,7 @@
         <v>4</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="F92" s="1" t="n">
         <v>129</v>
@@ -9072,7 +9072,7 @@
         <v>6</v>
       </c>
       <c r="L92" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M92" s="1" t="n">
         <v>92</v>
@@ -9096,7 +9096,7 @@
         </is>
       </c>
       <c r="R92" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S92" s="1" t="n">
         <v>1</v>
@@ -9123,7 +9123,7 @@
         </is>
       </c>
       <c r="Y92" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z92" s="1" t="n">
         <v>82</v>
@@ -9152,7 +9152,7 @@
         <v>15</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F93" s="1" t="n">
         <v>144</v>
@@ -9179,7 +9179,7 @@
         <v>10</v>
       </c>
       <c r="L93" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M93" s="1" t="n">
         <v>106</v>
@@ -9203,10 +9203,10 @@
         </is>
       </c>
       <c r="R93" s="1" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="S93" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="T93" s="1" t="n">
         <v>163</v>
@@ -9230,7 +9230,7 @@
         </is>
       </c>
       <c r="Y93" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z93" s="1" t="n">
         <v>93</v>
@@ -9259,7 +9259,7 @@
         <v>8</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F94" s="1" t="n">
         <v>144</v>
@@ -9286,7 +9286,7 @@
         <v>6</v>
       </c>
       <c r="L94" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M94" s="1" t="n">
         <v>97</v>
@@ -9310,10 +9310,10 @@
         </is>
       </c>
       <c r="R94" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S94" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T94" s="1" t="n">
         <v>133</v>
@@ -9337,7 +9337,7 @@
         </is>
       </c>
       <c r="Y94" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z94" s="1" t="n">
         <v>85</v>
@@ -9417,10 +9417,10 @@
         </is>
       </c>
       <c r="R95" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S95" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T95" s="1" t="n">
         <v>156</v>
@@ -9473,7 +9473,7 @@
         <v>3</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="F96" s="1" t="n">
         <v>143</v>
@@ -9500,7 +9500,7 @@
         <v>1</v>
       </c>
       <c r="L96" s="1" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="M96" s="1" t="n">
         <v>101</v>
@@ -9527,7 +9527,7 @@
         <v>5</v>
       </c>
       <c r="S96" s="1" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T96" s="1" t="n">
         <v>141</v>
@@ -9551,7 +9551,7 @@
         </is>
       </c>
       <c r="Y96" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z96" s="1" t="n">
         <v>88</v>
@@ -9580,7 +9580,7 @@
         <v>5</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="F97" s="1" t="n">
         <v>105</v>
@@ -9607,7 +9607,7 @@
         <v>5</v>
       </c>
       <c r="L97" s="1" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="M97" s="1" t="n">
         <v>73</v>
@@ -9631,7 +9631,7 @@
         </is>
       </c>
       <c r="R97" s="1" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="S97" s="1" t="n">
         <v>3</v>
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="Y97" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Z97" s="1" t="n">
         <v>70</v>
@@ -9687,7 +9687,7 @@
         <v>36</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F98" s="1" t="n">
         <v>138</v>
@@ -9714,7 +9714,7 @@
         <v>35</v>
       </c>
       <c r="L98" s="1" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="M98" s="1" t="n">
         <v>107</v>
@@ -9738,10 +9738,10 @@
         </is>
       </c>
       <c r="R98" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="S98" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T98" s="1" t="n">
         <v>127</v>
@@ -9765,7 +9765,7 @@
         </is>
       </c>
       <c r="Y98" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Z98" s="1" t="n">
         <v>82</v>
@@ -9794,7 +9794,7 @@
         <v>58</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F99" s="1" t="n">
         <v>147</v>
@@ -9821,7 +9821,7 @@
         <v>48</v>
       </c>
       <c r="L99" s="1" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M99" s="1" t="n">
         <v>123</v>
@@ -9845,7 +9845,7 @@
         </is>
       </c>
       <c r="R99" s="1" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="S99" s="1" t="n">
         <v>56</v>
@@ -9872,7 +9872,7 @@
         </is>
       </c>
       <c r="Y99" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Z99" s="1" t="n">
         <v>79</v>
@@ -9901,7 +9901,7 @@
         <v>5</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F100" s="1" t="n">
         <v>116</v>
@@ -9928,7 +9928,7 @@
         <v>4</v>
       </c>
       <c r="L100" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M100" s="1" t="n">
         <v>81</v>
@@ -9952,10 +9952,10 @@
         </is>
       </c>
       <c r="R100" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="S100" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T100" s="1" t="n">
         <v>107</v>
@@ -9979,7 +9979,7 @@
         </is>
       </c>
       <c r="Y100" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z100" s="1" t="n">
         <v>74</v>
@@ -10008,7 +10008,7 @@
         <v>90</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F101" s="1" t="n">
         <v>149</v>
@@ -10035,7 +10035,7 @@
         <v>92</v>
       </c>
       <c r="L101" s="1" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M101" s="1" t="n">
         <v>133</v>
@@ -10059,10 +10059,10 @@
         </is>
       </c>
       <c r="R101" s="1" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="S101" s="1" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T101" s="1" t="n">
         <v>168</v>
@@ -10086,7 +10086,7 @@
         </is>
       </c>
       <c r="Y101" s="1" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Z101" s="1" t="n">
         <v>77</v>
@@ -10115,7 +10115,7 @@
         <v>2</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="F102" s="1" t="n">
         <v>112</v>
@@ -10142,7 +10142,7 @@
         <v>5</v>
       </c>
       <c r="L102" s="1" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M102" s="1" t="n">
         <v>79</v>
@@ -10169,7 +10169,7 @@
         <v>5</v>
       </c>
       <c r="S102" s="1" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T102" s="1" t="n">
         <v>132</v>
@@ -10193,7 +10193,7 @@
         </is>
       </c>
       <c r="Y102" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z102" s="1" t="n">
         <v>71</v>
@@ -10329,7 +10329,7 @@
         <v>1</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="F104" s="1" t="n">
         <v>22</v>
@@ -10356,7 +10356,7 @@
         <v>2</v>
       </c>
       <c r="L104" s="1" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M104" s="1" t="n">
         <v>22</v>
@@ -10383,7 +10383,7 @@
         <v>0</v>
       </c>
       <c r="S104" s="1" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="T104" s="1" t="n">
         <v>22</v>
@@ -10407,7 +10407,7 @@
         </is>
       </c>
       <c r="Y104" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z104" s="1" t="n">
         <v>24</v>
@@ -10487,10 +10487,10 @@
         </is>
       </c>
       <c r="R105" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="S105" s="1" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="T105" s="1" t="n">
         <v>45</v>
@@ -10594,10 +10594,10 @@
         </is>
       </c>
       <c r="R106" s="1" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S106" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T106" s="1" t="n">
         <v>162</v>
@@ -10701,10 +10701,10 @@
         </is>
       </c>
       <c r="R107" s="1" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="S107" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T107" s="1" t="n">
         <v>134</v>
@@ -10757,7 +10757,7 @@
         <v>50</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F108" s="1" t="n">
         <v>103</v>
@@ -10784,7 +10784,7 @@
         <v>52</v>
       </c>
       <c r="L108" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M108" s="1" t="n">
         <v>96</v>
@@ -10808,10 +10808,10 @@
         </is>
       </c>
       <c r="R108" s="1" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="S108" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="T108" s="1" t="n">
         <v>150</v>
@@ -10835,7 +10835,7 @@
         </is>
       </c>
       <c r="Y108" s="1" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="Z108" s="1" t="n">
         <v>93</v>
@@ -10864,7 +10864,7 @@
         <v>59</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F109" s="1" t="n">
         <v>107</v>
@@ -10891,7 +10891,7 @@
         <v>55</v>
       </c>
       <c r="L109" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M109" s="1" t="n">
         <v>99</v>
@@ -10918,7 +10918,7 @@
         <v>74</v>
       </c>
       <c r="S109" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="T109" s="1" t="n">
         <v>124</v>
@@ -10942,7 +10942,7 @@
         </is>
       </c>
       <c r="Y109" s="1" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z109" s="1" t="n">
         <v>98</v>
@@ -11022,10 +11022,10 @@
         </is>
       </c>
       <c r="R110" s="1" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="S110" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="T110" s="1" t="n">
         <v>148</v>
@@ -11129,10 +11129,10 @@
         </is>
       </c>
       <c r="R111" s="1" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="S111" s="1" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="T111" s="1" t="n">
         <v>137</v>
@@ -11185,7 +11185,7 @@
         <v>51</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="F112" s="1" t="n">
         <v>115</v>
@@ -11212,7 +11212,7 @@
         <v>54</v>
       </c>
       <c r="L112" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M112" s="1" t="n">
         <v>103</v>
@@ -11236,10 +11236,10 @@
         </is>
       </c>
       <c r="R112" s="1" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="S112" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T112" s="1" t="n">
         <v>122</v>
@@ -11263,7 +11263,7 @@
         </is>
       </c>
       <c r="Y112" s="1" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="Z112" s="1" t="n">
         <v>93</v>
@@ -11450,10 +11450,10 @@
         </is>
       </c>
       <c r="R114" s="1" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="S114" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T114" s="1" t="n">
         <v>109</v>
@@ -11506,7 +11506,7 @@
         <v>52</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="F115" s="1" t="n">
         <v>111</v>
@@ -11533,7 +11533,7 @@
         <v>55</v>
       </c>
       <c r="L115" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M115" s="1" t="n">
         <v>109</v>
@@ -11557,10 +11557,10 @@
         </is>
       </c>
       <c r="R115" s="1" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="S115" s="1" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="T115" s="1" t="n">
         <v>172</v>
@@ -11584,7 +11584,7 @@
         </is>
       </c>
       <c r="Y115" s="1" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z115" s="1" t="n">
         <v>98</v>
@@ -11613,7 +11613,7 @@
         <v>58</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F116" s="1" t="n">
         <v>119</v>
@@ -11640,7 +11640,7 @@
         <v>57</v>
       </c>
       <c r="L116" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M116" s="1" t="n">
         <v>98</v>
@@ -11664,7 +11664,7 @@
         </is>
       </c>
       <c r="R116" s="1" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="S116" s="1" t="n">
         <v>22</v>
@@ -11691,7 +11691,7 @@
         </is>
       </c>
       <c r="Y116" s="1" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Z116" s="1" t="n">
         <v>96</v>
@@ -11720,7 +11720,7 @@
         <v>16</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="F117" s="1" t="n">
         <v>83</v>
@@ -11747,7 +11747,7 @@
         <v>18</v>
       </c>
       <c r="L117" s="1" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="M117" s="1" t="n">
         <v>60</v>
@@ -11771,10 +11771,10 @@
         </is>
       </c>
       <c r="R117" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="S117" s="1" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="T117" s="1" t="n">
         <v>58</v>
@@ -11798,7 +11798,7 @@
         </is>
       </c>
       <c r="Y117" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z117" s="1" t="n">
         <v>56</v>
@@ -11827,7 +11827,7 @@
         <v>11</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="F118" s="1" t="n">
         <v>32</v>
@@ -11854,7 +11854,7 @@
         <v>11</v>
       </c>
       <c r="L118" s="1" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="M118" s="1" t="n">
         <v>32</v>
@@ -11881,7 +11881,7 @@
         <v>10</v>
       </c>
       <c r="S118" s="1" t="n">
-        <v>-11</v>
+        <v>-9</v>
       </c>
       <c r="T118" s="1" t="n">
         <v>31</v>
@@ -11905,7 +11905,7 @@
         </is>
       </c>
       <c r="Y118" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Z118" s="1" t="n">
         <v>40</v>
@@ -11934,7 +11934,7 @@
         <v>3</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="F119" s="1" t="n">
         <v>4</v>
@@ -11961,7 +11961,7 @@
         <v>3</v>
       </c>
       <c r="L119" s="1" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="M119" s="1" t="n">
         <v>6</v>
@@ -11985,7 +11985,7 @@
         </is>
       </c>
       <c r="R119" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S119" s="1" t="n">
         <v>-8</v>
@@ -12012,7 +12012,7 @@
         </is>
       </c>
       <c r="Y119" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z119" s="1" t="n">
         <v>10</v>
@@ -12092,10 +12092,10 @@
         </is>
       </c>
       <c r="R120" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S120" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T120" s="1" t="n">
         <v>76</v>
@@ -12148,7 +12148,7 @@
         <v>9</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F121" s="1" t="n">
         <v>88</v>
@@ -12175,7 +12175,7 @@
         <v>8</v>
       </c>
       <c r="L121" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M121" s="1" t="n">
         <v>51</v>
@@ -12199,10 +12199,10 @@
         </is>
       </c>
       <c r="R121" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S121" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T121" s="1" t="n">
         <v>47</v>
@@ -12226,7 +12226,7 @@
         </is>
       </c>
       <c r="Y121" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z121" s="1" t="n">
         <v>80</v>
@@ -12255,7 +12255,7 @@
         <v>11</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F122" s="1" t="n">
         <v>19</v>
@@ -12282,7 +12282,7 @@
         <v>9</v>
       </c>
       <c r="L122" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M122" s="1" t="n">
         <v>16</v>
@@ -12306,7 +12306,7 @@
         </is>
       </c>
       <c r="R122" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S122" s="1" t="n">
         <v>-1</v>
@@ -12333,7 +12333,7 @@
         </is>
       </c>
       <c r="Y122" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z122" s="1" t="n">
         <v>11</v>
@@ -12469,7 +12469,7 @@
         <v>10</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="F124" s="1" t="n">
         <v>157</v>
@@ -12496,7 +12496,7 @@
         <v>10</v>
       </c>
       <c r="L124" s="1" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="M124" s="1" t="n">
         <v>108</v>
@@ -12520,7 +12520,7 @@
         </is>
       </c>
       <c r="R124" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="S124" s="1" t="n">
         <v>1</v>
@@ -12547,7 +12547,7 @@
         </is>
       </c>
       <c r="Y124" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z124" s="1" t="n">
         <v>94</v>
@@ -12576,7 +12576,7 @@
         <v>6</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="F125" s="1" t="n">
         <v>147</v>
@@ -12603,7 +12603,7 @@
         <v>5</v>
       </c>
       <c r="L125" s="1" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="M125" s="1" t="n">
         <v>105</v>
@@ -12627,7 +12627,7 @@
         </is>
       </c>
       <c r="R125" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S125" s="1" t="n">
         <v>1</v>
@@ -12654,7 +12654,7 @@
         </is>
       </c>
       <c r="Y125" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z125" s="1" t="n">
         <v>94</v>
@@ -12683,7 +12683,7 @@
         <v>4</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="F126" s="1" t="n">
         <v>110</v>
@@ -12710,7 +12710,7 @@
         <v>4</v>
       </c>
       <c r="L126" s="1" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="M126" s="1" t="n">
         <v>72</v>
@@ -12734,10 +12734,10 @@
         </is>
       </c>
       <c r="R126" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S126" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T126" s="1" t="n">
         <v>125</v>
@@ -12761,7 +12761,7 @@
         </is>
       </c>
       <c r="Y126" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z126" s="1" t="n">
         <v>74</v>
@@ -12841,10 +12841,10 @@
         </is>
       </c>
       <c r="R127" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S127" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T127" s="1" t="n">
         <v>41</v>
@@ -12897,7 +12897,7 @@
         <v>14</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F128" s="1" t="n">
         <v>95</v>
@@ -12924,7 +12924,7 @@
         <v>9</v>
       </c>
       <c r="L128" s="1" t="n">
-        <v>-3</v>
+        <v>5</v>
       </c>
       <c r="M128" s="1" t="n">
         <v>73</v>
@@ -12948,10 +12948,10 @@
         </is>
       </c>
       <c r="R128" s="1" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="S128" s="1" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T128" s="1" t="n">
         <v>102</v>
@@ -12975,7 +12975,7 @@
         </is>
       </c>
       <c r="Y128" s="1" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="Z128" s="1" t="n">
         <v>67</v>
@@ -13004,7 +13004,7 @@
         <v>4</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="F129" s="1" t="n">
         <v>79</v>
@@ -13031,7 +13031,7 @@
         <v>4</v>
       </c>
       <c r="L129" s="1" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="M129" s="1" t="n">
         <v>44</v>
@@ -13055,7 +13055,7 @@
         </is>
       </c>
       <c r="R129" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S129" s="1" t="n">
         <v>-3</v>
@@ -13082,7 +13082,7 @@
         </is>
       </c>
       <c r="Y129" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z129" s="1" t="n">
         <v>66</v>
@@ -13162,10 +13162,10 @@
         </is>
       </c>
       <c r="R130" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S130" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T130" s="1" t="n">
         <v>62</v>
@@ -13218,7 +13218,7 @@
         <v>5</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="F131" s="1" t="n">
         <v>103</v>
@@ -13245,7 +13245,7 @@
         <v>4</v>
       </c>
       <c r="L131" s="1" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="M131" s="1" t="n">
         <v>65</v>
@@ -13269,7 +13269,7 @@
         </is>
       </c>
       <c r="R131" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S131" s="1" t="n">
         <v>-2</v>
@@ -13296,7 +13296,7 @@
         </is>
       </c>
       <c r="Y131" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z131" s="1" t="n">
         <v>86</v>
@@ -13325,7 +13325,7 @@
         <v>11</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F132" s="1" t="n">
         <v>136</v>
@@ -13352,7 +13352,7 @@
         <v>10</v>
       </c>
       <c r="L132" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M132" s="1" t="n">
         <v>96</v>
@@ -13376,10 +13376,10 @@
         </is>
       </c>
       <c r="R132" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="S132" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T132" s="1" t="n">
         <v>143</v>
@@ -13403,7 +13403,7 @@
         </is>
       </c>
       <c r="Y132" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z132" s="1" t="n">
         <v>92</v>
@@ -13432,7 +13432,7 @@
         <v>37</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>-15</v>
+        <v>8</v>
       </c>
       <c r="F133" s="1" t="n">
         <v>116</v>
@@ -13459,7 +13459,7 @@
         <v>37</v>
       </c>
       <c r="L133" s="1" t="n">
-        <v>-15</v>
+        <v>8</v>
       </c>
       <c r="M133" s="1" t="n">
         <v>116</v>
@@ -13483,10 +13483,10 @@
         </is>
       </c>
       <c r="R133" s="1" t="n">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="S133" s="1" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="T133" s="1" t="n">
         <v>202</v>
@@ -13510,7 +13510,7 @@
         </is>
       </c>
       <c r="Y133" s="1" t="n">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="Z133" s="1" t="n">
         <v>123</v>
@@ -13539,7 +13539,7 @@
         <v>9</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F134" s="1" t="n">
         <v>106</v>
@@ -13566,7 +13566,7 @@
         <v>6</v>
       </c>
       <c r="L134" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M134" s="1" t="n">
         <v>67</v>
@@ -13593,7 +13593,7 @@
         <v>6</v>
       </c>
       <c r="S134" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T134" s="1" t="n">
         <v>63</v>
@@ -13617,7 +13617,7 @@
         </is>
       </c>
       <c r="Y134" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z134" s="1" t="n">
         <v>91</v>
@@ -13753,7 +13753,7 @@
         <v>5</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="F136" s="1" t="n">
         <v>47</v>
@@ -13780,7 +13780,7 @@
         <v>5</v>
       </c>
       <c r="L136" s="1" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="M136" s="1" t="n">
         <v>32</v>
@@ -13804,10 +13804,10 @@
         </is>
       </c>
       <c r="R136" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S136" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T136" s="1" t="n">
         <v>30</v>
@@ -13831,7 +13831,7 @@
         </is>
       </c>
       <c r="Y136" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Z136" s="1" t="n">
         <v>62</v>
@@ -13860,7 +13860,7 @@
         <v>18</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F137" s="1" t="n">
         <v>144</v>
@@ -13887,7 +13887,7 @@
         <v>16</v>
       </c>
       <c r="L137" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M137" s="1" t="n">
         <v>109</v>
@@ -13911,10 +13911,10 @@
         </is>
       </c>
       <c r="R137" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S137" s="1" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T137" s="1" t="n">
         <v>167</v>
@@ -13938,7 +13938,7 @@
         </is>
       </c>
       <c r="Y137" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Z137" s="1" t="n">
         <v>90</v>
@@ -13967,7 +13967,7 @@
         <v>10</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F138" s="1" t="n">
         <v>86</v>
@@ -13994,7 +13994,7 @@
         <v>9</v>
       </c>
       <c r="L138" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M138" s="1" t="n">
         <v>53</v>
@@ -14018,10 +14018,10 @@
         </is>
       </c>
       <c r="R138" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="S138" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T138" s="1" t="n">
         <v>49</v>
@@ -14045,7 +14045,7 @@
         </is>
       </c>
       <c r="Y138" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z138" s="1" t="n">
         <v>79</v>
@@ -14074,7 +14074,7 @@
         <v>18</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F139" s="1" t="n">
         <v>96</v>
@@ -14101,7 +14101,7 @@
         <v>9</v>
       </c>
       <c r="L139" s="1" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="M139" s="1" t="n">
         <v>59</v>
@@ -14125,7 +14125,7 @@
         </is>
       </c>
       <c r="R139" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S139" s="1" t="n">
         <v>-5</v>
@@ -14152,7 +14152,7 @@
         </is>
       </c>
       <c r="Y139" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z139" s="1" t="n">
         <v>63</v>
@@ -14232,10 +14232,10 @@
         </is>
       </c>
       <c r="R140" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S140" s="1" t="n">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="T140" s="1" t="n">
         <v>6</v>
@@ -14288,7 +14288,7 @@
         <v>8</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F141" s="1" t="n">
         <v>68</v>
@@ -14315,7 +14315,7 @@
         <v>6</v>
       </c>
       <c r="L141" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M141" s="1" t="n">
         <v>42</v>
@@ -14339,10 +14339,10 @@
         </is>
       </c>
       <c r="R141" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S141" s="1" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="T141" s="1" t="n">
         <v>41</v>
@@ -14366,7 +14366,7 @@
         </is>
       </c>
       <c r="Y141" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z141" s="1" t="n">
         <v>82</v>
@@ -14395,7 +14395,7 @@
         <v>7</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F142" s="1" t="n">
         <v>95</v>
@@ -14422,7 +14422,7 @@
         <v>7</v>
       </c>
       <c r="L142" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M142" s="1" t="n">
         <v>56</v>
@@ -14446,10 +14446,10 @@
         </is>
       </c>
       <c r="R142" s="1" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="S142" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T142" s="1" t="n">
         <v>57</v>
@@ -14473,7 +14473,7 @@
         </is>
       </c>
       <c r="Y142" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z142" s="1" t="n">
         <v>75</v>
@@ -14502,7 +14502,7 @@
         <v>6</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F143" s="1" t="n">
         <v>87</v>
@@ -14529,7 +14529,7 @@
         <v>4</v>
       </c>
       <c r="L143" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M143" s="1" t="n">
         <v>49</v>
@@ -14553,10 +14553,10 @@
         </is>
       </c>
       <c r="R143" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S143" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T143" s="1" t="n">
         <v>48</v>
@@ -14580,7 +14580,7 @@
         </is>
       </c>
       <c r="Y143" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z143" s="1" t="n">
         <v>73</v>
@@ -14609,7 +14609,7 @@
         <v>36</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>-5</v>
+        <v>13</v>
       </c>
       <c r="F144" s="1" t="n">
         <v>86</v>
@@ -14636,7 +14636,7 @@
         <v>36</v>
       </c>
       <c r="L144" s="1" t="n">
-        <v>-5</v>
+        <v>13</v>
       </c>
       <c r="M144" s="1" t="n">
         <v>85</v>
@@ -14660,10 +14660,10 @@
         </is>
       </c>
       <c r="R144" s="1" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="S144" s="1" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="T144" s="1" t="n">
         <v>93</v>
@@ -14687,7 +14687,7 @@
         </is>
       </c>
       <c r="Y144" s="1" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="Z144" s="1" t="n">
         <v>90</v>
@@ -14716,7 +14716,7 @@
         <v>6</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F145" s="1" t="n">
         <v>55</v>
@@ -14743,7 +14743,7 @@
         <v>5</v>
       </c>
       <c r="L145" s="1" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M145" s="1" t="n">
         <v>30</v>
@@ -14767,10 +14767,10 @@
         </is>
       </c>
       <c r="R145" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S145" s="1" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="T145" s="1" t="n">
         <v>29</v>
@@ -14794,7 +14794,7 @@
         </is>
       </c>
       <c r="Y145" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z145" s="1" t="n">
         <v>67</v>
@@ -14823,7 +14823,7 @@
         <v>14</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F146" s="1" t="n">
         <v>133</v>
@@ -14850,7 +14850,7 @@
         <v>12</v>
       </c>
       <c r="L146" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M146" s="1" t="n">
         <v>103</v>
@@ -14874,10 +14874,10 @@
         </is>
       </c>
       <c r="R146" s="1" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="S146" s="1" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="T146" s="1" t="n">
         <v>153</v>
@@ -14901,7 +14901,7 @@
         </is>
       </c>
       <c r="Y146" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z146" s="1" t="n">
         <v>93</v>
@@ -14981,10 +14981,10 @@
         </is>
       </c>
       <c r="R147" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="S147" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T147" s="1" t="n">
         <v>63</v>
@@ -15037,7 +15037,7 @@
         <v>16</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F148" s="1" t="n">
         <v>76</v>
@@ -15064,7 +15064,7 @@
         <v>10</v>
       </c>
       <c r="L148" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M148" s="1" t="n">
         <v>53</v>
@@ -15088,10 +15088,10 @@
         </is>
       </c>
       <c r="R148" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="S148" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T148" s="1" t="n">
         <v>54</v>
@@ -15115,7 +15115,7 @@
         </is>
       </c>
       <c r="Y148" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z148" s="1" t="n">
         <v>74</v>
@@ -15195,10 +15195,10 @@
         </is>
       </c>
       <c r="R149" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S149" s="1" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="T149" s="1" t="n">
         <v>35</v>
@@ -15251,7 +15251,7 @@
         <v>11</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F150" s="1" t="n">
         <v>61</v>
@@ -15278,7 +15278,7 @@
         <v>6</v>
       </c>
       <c r="L150" s="1" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="M150" s="1" t="n">
         <v>50</v>
@@ -15302,10 +15302,10 @@
         </is>
       </c>
       <c r="R150" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S150" s="1" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="T150" s="1" t="n">
         <v>49</v>
@@ -15329,7 +15329,7 @@
         </is>
       </c>
       <c r="Y150" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Z150" s="1" t="n">
         <v>74</v>
@@ -15358,7 +15358,7 @@
         <v>10</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F151" s="1" t="n">
         <v>90</v>
@@ -15385,7 +15385,7 @@
         <v>9</v>
       </c>
       <c r="L151" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M151" s="1" t="n">
         <v>51</v>
@@ -15409,10 +15409,10 @@
         </is>
       </c>
       <c r="R151" s="1" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="S151" s="1" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T151" s="1" t="n">
         <v>52</v>
@@ -15436,7 +15436,7 @@
         </is>
       </c>
       <c r="Y151" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z151" s="1" t="n">
         <v>74</v>
@@ -15465,7 +15465,7 @@
         <v>7</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F152" s="1" t="n">
         <v>63</v>
@@ -15492,7 +15492,7 @@
         <v>4</v>
       </c>
       <c r="L152" s="1" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M152" s="1" t="n">
         <v>36</v>
@@ -15516,7 +15516,7 @@
         </is>
       </c>
       <c r="R152" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S152" s="1" t="n">
         <v>-3</v>
@@ -15543,7 +15543,7 @@
         </is>
       </c>
       <c r="Y152" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z152" s="1" t="n">
         <v>80</v>
@@ -15623,10 +15623,10 @@
         </is>
       </c>
       <c r="R153" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S153" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T153" s="1" t="n">
         <v>62</v>
@@ -15679,7 +15679,7 @@
         <v>8</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F154" s="1" t="n">
         <v>150</v>
@@ -15706,7 +15706,7 @@
         <v>10</v>
       </c>
       <c r="L154" s="1" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="M154" s="1" t="n">
         <v>111</v>
@@ -15733,7 +15733,7 @@
         <v>12</v>
       </c>
       <c r="S154" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T154" s="1" t="n">
         <v>173</v>
@@ -15757,7 +15757,7 @@
         </is>
       </c>
       <c r="Y154" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Z154" s="1" t="n">
         <v>96</v>
@@ -15786,7 +15786,7 @@
         <v>1</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="F155" s="1" t="n">
         <v>3</v>
@@ -15813,7 +15813,7 @@
         <v>1</v>
       </c>
       <c r="L155" s="1" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="M155" s="1" t="n">
         <v>3</v>
@@ -15840,7 +15840,7 @@
         <v>2</v>
       </c>
       <c r="S155" s="1" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="T155" s="1" t="n">
         <v>4</v>
@@ -15864,7 +15864,7 @@
         </is>
       </c>
       <c r="Y155" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z155" s="1" t="n">
         <v>7</v>
@@ -15893,7 +15893,7 @@
         <v>13</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F156" s="1" t="n">
         <v>146</v>
@@ -15920,7 +15920,7 @@
         <v>13</v>
       </c>
       <c r="L156" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M156" s="1" t="n">
         <v>108</v>
@@ -15944,10 +15944,10 @@
         </is>
       </c>
       <c r="R156" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S156" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T156" s="1" t="n">
         <v>142</v>
@@ -15971,7 +15971,7 @@
         </is>
       </c>
       <c r="Y156" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z156" s="1" t="n">
         <v>87</v>
@@ -16000,7 +16000,7 @@
         <v>7</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="F157" s="1" t="n">
         <v>101</v>
@@ -16027,7 +16027,7 @@
         <v>5</v>
       </c>
       <c r="L157" s="1" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="M157" s="1" t="n">
         <v>61</v>
@@ -16054,7 +16054,7 @@
         <v>4</v>
       </c>
       <c r="S157" s="1" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="T157" s="1" t="n">
         <v>59</v>
@@ -16078,7 +16078,7 @@
         </is>
       </c>
       <c r="Y157" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z157" s="1" t="n">
         <v>92</v>
@@ -16107,7 +16107,7 @@
         <v>30</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F158" s="1" t="n">
         <v>146</v>
@@ -16134,7 +16134,7 @@
         <v>27</v>
       </c>
       <c r="L158" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M158" s="1" t="n">
         <v>105</v>
@@ -16158,10 +16158,10 @@
         </is>
       </c>
       <c r="R158" s="1" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="S158" s="1" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="T158" s="1" t="n">
         <v>139</v>
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="Y158" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z158" s="1" t="n">
         <v>87</v>
@@ -16214,7 +16214,7 @@
         <v>12</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F159" s="1" t="n">
         <v>102</v>
@@ -16241,7 +16241,7 @@
         <v>11</v>
       </c>
       <c r="L159" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M159" s="1" t="n">
         <v>62</v>
@@ -16265,10 +16265,10 @@
         </is>
       </c>
       <c r="R159" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="S159" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T159" s="1" t="n">
         <v>60</v>
@@ -16292,7 +16292,7 @@
         </is>
       </c>
       <c r="Y159" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z159" s="1" t="n">
         <v>72</v>
@@ -16321,7 +16321,7 @@
         <v>4</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="F160" s="1" t="n">
         <v>91</v>
@@ -16348,7 +16348,7 @@
         <v>3</v>
       </c>
       <c r="L160" s="1" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="M160" s="1" t="n">
         <v>71</v>
@@ -16375,7 +16375,7 @@
         <v>4</v>
       </c>
       <c r="S160" s="1" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="T160" s="1" t="n">
         <v>108</v>
@@ -16399,7 +16399,7 @@
         </is>
       </c>
       <c r="Y160" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z160" s="1" t="n">
         <v>70</v>
@@ -16428,7 +16428,7 @@
         <v>4</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F161" s="1" t="n">
         <v>63</v>
@@ -16455,7 +16455,7 @@
         <v>5</v>
       </c>
       <c r="L161" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M161" s="1" t="n">
         <v>39</v>
@@ -16482,7 +16482,7 @@
         <v>2</v>
       </c>
       <c r="S161" s="1" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="T161" s="1" t="n">
         <v>35</v>
@@ -16506,7 +16506,7 @@
         </is>
       </c>
       <c r="Y161" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z161" s="1" t="n">
         <v>68</v>
@@ -16535,7 +16535,7 @@
         <v>11</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F162" s="1" t="n">
         <v>100</v>
@@ -16562,7 +16562,7 @@
         <v>9</v>
       </c>
       <c r="L162" s="1" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="M162" s="1" t="n">
         <v>63</v>
@@ -16586,10 +16586,10 @@
         </is>
       </c>
       <c r="R162" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="S162" s="1" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T162" s="1" t="n">
         <v>64</v>
@@ -16613,7 +16613,7 @@
         </is>
       </c>
       <c r="Y162" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z162" s="1" t="n">
         <v>77</v>
@@ -16693,10 +16693,10 @@
         </is>
       </c>
       <c r="R163" s="1" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="S163" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T163" s="1" t="n">
         <v>154</v>
@@ -16749,7 +16749,7 @@
         <v>7</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F164" s="1" t="n">
         <v>75</v>
@@ -16776,7 +16776,7 @@
         <v>6</v>
       </c>
       <c r="L164" s="1" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M164" s="1" t="n">
         <v>48</v>
@@ -16800,10 +16800,10 @@
         </is>
       </c>
       <c r="R164" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S164" s="1" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="T164" s="1" t="n">
         <v>47</v>
@@ -16827,7 +16827,7 @@
         </is>
       </c>
       <c r="Y164" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z164" s="1" t="n">
         <v>79</v>
@@ -16856,7 +16856,7 @@
         <v>1</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F165" s="1" t="n">
         <v>66</v>
@@ -16883,7 +16883,7 @@
         <v>2</v>
       </c>
       <c r="L165" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M165" s="1" t="n">
         <v>45</v>
@@ -16910,7 +16910,7 @@
         <v>1</v>
       </c>
       <c r="S165" s="1" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T165" s="1" t="n">
         <v>67</v>
@@ -16934,7 +16934,7 @@
         </is>
       </c>
       <c r="Y165" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z165" s="1" t="n">
         <v>44</v>
@@ -17070,7 +17070,7 @@
         <v>2</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="F167" s="1" t="n">
         <v>65</v>
@@ -17097,7 +17097,7 @@
         <v>2</v>
       </c>
       <c r="L167" s="1" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="M167" s="1" t="n">
         <v>46</v>
@@ -17124,7 +17124,7 @@
         <v>3</v>
       </c>
       <c r="S167" s="1" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T167" s="1" t="n">
         <v>66</v>
@@ -17148,7 +17148,7 @@
         </is>
       </c>
       <c r="Y167" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z167" s="1" t="n">
         <v>43</v>
@@ -17177,7 +17177,7 @@
         <v>9</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F168" s="1" t="n">
         <v>149</v>
@@ -17204,7 +17204,7 @@
         <v>5</v>
       </c>
       <c r="L168" s="1" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="M168" s="1" t="n">
         <v>107</v>
@@ -17231,7 +17231,7 @@
         <v>9</v>
       </c>
       <c r="S168" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T168" s="1" t="n">
         <v>168</v>
@@ -17255,7 +17255,7 @@
         </is>
       </c>
       <c r="Y168" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z168" s="1" t="n">
         <v>87</v>
@@ -17284,7 +17284,7 @@
         <v>6</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F169" s="1" t="n">
         <v>138</v>
@@ -17311,7 +17311,7 @@
         <v>7</v>
       </c>
       <c r="L169" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M169" s="1" t="n">
         <v>100</v>
@@ -17338,7 +17338,7 @@
         <v>8</v>
       </c>
       <c r="S169" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T169" s="1" t="n">
         <v>140</v>
@@ -17362,7 +17362,7 @@
         </is>
       </c>
       <c r="Y169" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z169" s="1" t="n">
         <v>89</v>
@@ -17391,7 +17391,7 @@
         <v>8</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F170" s="1" t="n">
         <v>126</v>
@@ -17418,7 +17418,7 @@
         <v>5</v>
       </c>
       <c r="L170" s="1" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="M170" s="1" t="n">
         <v>94</v>
@@ -17442,7 +17442,7 @@
         </is>
       </c>
       <c r="R170" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S170" s="1" t="n">
         <v>0</v>
@@ -17469,7 +17469,7 @@
         </is>
       </c>
       <c r="Y170" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z170" s="1" t="n">
         <v>85</v>
@@ -17498,7 +17498,7 @@
         <v>13</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="F171" s="1" t="n">
         <v>103</v>
@@ -17525,7 +17525,7 @@
         <v>14</v>
       </c>
       <c r="L171" s="1" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M171" s="1" t="n">
         <v>98</v>
@@ -17552,7 +17552,7 @@
         <v>10</v>
       </c>
       <c r="S171" s="1" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="T171" s="1" t="n">
         <v>97</v>
@@ -17576,7 +17576,7 @@
         </is>
       </c>
       <c r="Y171" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z171" s="1" t="n">
         <v>96</v>
@@ -17605,7 +17605,7 @@
         <v>5</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F172" s="1" t="n">
         <v>140</v>
@@ -17632,7 +17632,7 @@
         <v>7</v>
       </c>
       <c r="L172" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M172" s="1" t="n">
         <v>99</v>
@@ -17656,7 +17656,7 @@
         </is>
       </c>
       <c r="R172" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="S172" s="1" t="n">
         <v>8</v>
@@ -17683,7 +17683,7 @@
         </is>
       </c>
       <c r="Y172" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z172" s="1" t="n">
         <v>88</v>
@@ -17819,7 +17819,7 @@
         <v>2</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F174" s="1" t="n">
         <v>75</v>
@@ -17846,7 +17846,7 @@
         <v>2</v>
       </c>
       <c r="L174" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M174" s="1" t="n">
         <v>57</v>
@@ -17873,7 +17873,7 @@
         <v>2</v>
       </c>
       <c r="S174" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T174" s="1" t="n">
         <v>85</v>
@@ -17897,7 +17897,7 @@
         </is>
       </c>
       <c r="Y174" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z174" s="1" t="n">
         <v>51</v>
@@ -17977,10 +17977,10 @@
         </is>
       </c>
       <c r="R175" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S175" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T175" s="1" t="n">
         <v>63</v>
@@ -18033,7 +18033,7 @@
         <v>2</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="F176" s="1" t="n">
         <v>148</v>
@@ -18060,7 +18060,7 @@
         <v>3</v>
       </c>
       <c r="L176" s="1" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="M176" s="1" t="n">
         <v>107</v>
@@ -18084,10 +18084,10 @@
         </is>
       </c>
       <c r="R176" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S176" s="1" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="T176" s="1" t="n">
         <v>168</v>
@@ -18111,7 +18111,7 @@
         </is>
       </c>
       <c r="Y176" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z176" s="1" t="n">
         <v>89</v>
@@ -18140,7 +18140,7 @@
         <v>4</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F177" s="1" t="n">
         <v>30</v>
@@ -18167,7 +18167,7 @@
         <v>2</v>
       </c>
       <c r="L177" s="1" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M177" s="1" t="n">
         <v>29</v>
@@ -18194,7 +18194,7 @@
         <v>2</v>
       </c>
       <c r="S177" s="1" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T177" s="1" t="n">
         <v>28</v>
@@ -18218,7 +18218,7 @@
         </is>
       </c>
       <c r="Y177" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z177" s="1" t="n">
         <v>28</v>
@@ -18247,7 +18247,7 @@
         <v>4</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="F178" s="1" t="n">
         <v>144</v>
@@ -18274,7 +18274,7 @@
         <v>4</v>
       </c>
       <c r="L178" s="1" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="M178" s="1" t="n">
         <v>106</v>
@@ -18301,7 +18301,7 @@
         <v>5</v>
       </c>
       <c r="S178" s="1" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T178" s="1" t="n">
         <v>145</v>
@@ -18325,7 +18325,7 @@
         </is>
       </c>
       <c r="Y178" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z178" s="1" t="n">
         <v>88</v>
@@ -18354,7 +18354,7 @@
         <v>2</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="F179" s="1" t="n">
         <v>91</v>
@@ -18381,7 +18381,7 @@
         <v>5</v>
       </c>
       <c r="L179" s="1" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M179" s="1" t="n">
         <v>68</v>
@@ -18408,7 +18408,7 @@
         <v>10</v>
       </c>
       <c r="S179" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T179" s="1" t="n">
         <v>102</v>
@@ -18432,7 +18432,7 @@
         </is>
       </c>
       <c r="Y179" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z179" s="1" t="n">
         <v>64</v>
@@ -18461,7 +18461,7 @@
         <v>6</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F180" s="1" t="n">
         <v>97</v>
@@ -18488,7 +18488,7 @@
         <v>5</v>
       </c>
       <c r="L180" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M180" s="1" t="n">
         <v>71</v>
@@ -18515,7 +18515,7 @@
         <v>4</v>
       </c>
       <c r="S180" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T180" s="1" t="n">
         <v>90</v>
@@ -18539,7 +18539,7 @@
         </is>
       </c>
       <c r="Y180" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z180" s="1" t="n">
         <v>65</v>
@@ -18568,7 +18568,7 @@
         <v>9</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F181" s="1" t="n">
         <v>133</v>
@@ -18595,7 +18595,7 @@
         <v>7</v>
       </c>
       <c r="L181" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M181" s="1" t="n">
         <v>98</v>
@@ -18619,10 +18619,10 @@
         </is>
       </c>
       <c r="R181" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="S181" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T181" s="1" t="n">
         <v>153</v>
@@ -18646,7 +18646,7 @@
         </is>
       </c>
       <c r="Y181" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z181" s="1" t="n">
         <v>88</v>
@@ -18675,7 +18675,7 @@
         <v>2</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="F182" s="1" t="n">
         <v>125</v>
@@ -18702,7 +18702,7 @@
         <v>2</v>
       </c>
       <c r="L182" s="1" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="M182" s="1" t="n">
         <v>86</v>
@@ -18726,7 +18726,7 @@
         </is>
       </c>
       <c r="R182" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S182" s="1" t="n">
         <v>-7</v>
@@ -18753,7 +18753,7 @@
         </is>
       </c>
       <c r="Y182" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z182" s="1" t="n">
         <v>84</v>
@@ -18889,7 +18889,7 @@
         <v>7</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F184" s="1" t="n">
         <v>99</v>
@@ -18916,7 +18916,7 @@
         <v>7</v>
       </c>
       <c r="L184" s="1" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M184" s="1" t="n">
         <v>72</v>
@@ -18940,10 +18940,10 @@
         </is>
       </c>
       <c r="R184" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="S184" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T184" s="1" t="n">
         <v>95</v>
@@ -18967,7 +18967,7 @@
         </is>
       </c>
       <c r="Y184" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z184" s="1" t="n">
         <v>56</v>
@@ -18996,7 +18996,7 @@
         <v>5</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F185" s="1" t="n">
         <v>152</v>
@@ -19023,7 +19023,7 @@
         <v>8</v>
       </c>
       <c r="L185" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M185" s="1" t="n">
         <v>115</v>
@@ -19047,10 +19047,10 @@
         </is>
       </c>
       <c r="R185" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="S185" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T185" s="1" t="n">
         <v>186</v>
@@ -19074,7 +19074,7 @@
         </is>
       </c>
       <c r="Y185" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z185" s="1" t="n">
         <v>101</v>
@@ -19103,7 +19103,7 @@
         <v>4</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F186" s="1" t="n">
         <v>126</v>
@@ -19130,7 +19130,7 @@
         <v>5</v>
       </c>
       <c r="L186" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M186" s="1" t="n">
         <v>92</v>
@@ -19157,7 +19157,7 @@
         <v>9</v>
       </c>
       <c r="S186" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T186" s="1" t="n">
         <v>122</v>
@@ -19181,7 +19181,7 @@
         </is>
       </c>
       <c r="Y186" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z186" s="1" t="n">
         <v>78</v>
@@ -19210,7 +19210,7 @@
         <v>9</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F187" s="1" t="n">
         <v>131</v>
@@ -19237,7 +19237,7 @@
         <v>11</v>
       </c>
       <c r="L187" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M187" s="1" t="n">
         <v>93</v>
@@ -19261,10 +19261,10 @@
         </is>
       </c>
       <c r="R187" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="S187" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T187" s="1" t="n">
         <v>139</v>
@@ -19288,7 +19288,7 @@
         </is>
       </c>
       <c r="Y187" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z187" s="1" t="n">
         <v>80</v>
@@ -19317,7 +19317,7 @@
         <v>8</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F188" s="1" t="n">
         <v>58</v>
@@ -19344,7 +19344,7 @@
         <v>12</v>
       </c>
       <c r="L188" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M188" s="1" t="n">
         <v>33</v>
@@ -19368,10 +19368,10 @@
         </is>
       </c>
       <c r="R188" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S188" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T188" s="1" t="n">
         <v>31</v>
@@ -19395,7 +19395,7 @@
         </is>
       </c>
       <c r="Y188" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z188" s="1" t="n">
         <v>28</v>
@@ -19531,7 +19531,7 @@
         <v>10</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F190" s="1" t="n">
         <v>123</v>
@@ -19558,7 +19558,7 @@
         <v>11</v>
       </c>
       <c r="L190" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M190" s="1" t="n">
         <v>85</v>
@@ -19582,7 +19582,7 @@
         </is>
       </c>
       <c r="R190" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S190" s="1" t="n">
         <v>10</v>
@@ -19609,7 +19609,7 @@
         </is>
       </c>
       <c r="Y190" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z190" s="1" t="n">
         <v>74</v>
@@ -19689,10 +19689,10 @@
         </is>
       </c>
       <c r="R191" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S191" s="1" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="T191" s="1" t="n">
         <v>107</v>
@@ -19796,10 +19796,10 @@
         </is>
       </c>
       <c r="R192" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="S192" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T192" s="1" t="n">
         <v>147</v>
@@ -19852,7 +19852,7 @@
         <v>19</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F193" s="1" t="n">
         <v>156</v>
@@ -19879,7 +19879,7 @@
         <v>14</v>
       </c>
       <c r="L193" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M193" s="1" t="n">
         <v>107</v>
@@ -19903,7 +19903,7 @@
         </is>
       </c>
       <c r="R193" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="S193" s="1" t="n">
         <v>5</v>
@@ -19930,7 +19930,7 @@
         </is>
       </c>
       <c r="Y193" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z193" s="1" t="n">
         <v>81</v>
@@ -20066,7 +20066,7 @@
         <v>7</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F195" s="1" t="n">
         <v>147</v>
@@ -20093,7 +20093,7 @@
         <v>7</v>
       </c>
       <c r="L195" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M195" s="1" t="n">
         <v>101</v>
@@ -20120,7 +20120,7 @@
         <v>6</v>
       </c>
       <c r="S195" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T195" s="1" t="n">
         <v>146</v>
@@ -20144,7 +20144,7 @@
         </is>
       </c>
       <c r="Y195" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z195" s="1" t="n">
         <v>95</v>
@@ -20224,10 +20224,10 @@
         </is>
       </c>
       <c r="R196" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="S196" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T196" s="1" t="n">
         <v>140</v>
@@ -20280,7 +20280,7 @@
         <v>10</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F197" s="1" t="n">
         <v>123</v>
@@ -20307,7 +20307,7 @@
         <v>9</v>
       </c>
       <c r="L197" s="1" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="M197" s="1" t="n">
         <v>85</v>
@@ -20331,10 +20331,10 @@
         </is>
       </c>
       <c r="R197" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S197" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T197" s="1" t="n">
         <v>121</v>
@@ -20358,7 +20358,7 @@
         </is>
       </c>
       <c r="Y197" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z197" s="1" t="n">
         <v>83</v>
@@ -20387,7 +20387,7 @@
         <v>5</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="F198" s="1" t="n">
         <v>104</v>
@@ -20414,7 +20414,7 @@
         <v>3</v>
       </c>
       <c r="L198" s="1" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="M198" s="1" t="n">
         <v>68</v>
@@ -20441,7 +20441,7 @@
         <v>4</v>
       </c>
       <c r="S198" s="1" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="T198" s="1" t="n">
         <v>111</v>
@@ -20465,7 +20465,7 @@
         </is>
       </c>
       <c r="Y198" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z198" s="1" t="n">
         <v>69</v>
@@ -20545,10 +20545,10 @@
         </is>
       </c>
       <c r="R199" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S199" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T199" s="1" t="n">
         <v>37</v>
@@ -20708,7 +20708,7 @@
         <v>9</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F201" s="1" t="n">
         <v>106</v>
@@ -20735,7 +20735,7 @@
         <v>10</v>
       </c>
       <c r="L201" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M201" s="1" t="n">
         <v>79</v>
@@ -20762,7 +20762,7 @@
         <v>12</v>
       </c>
       <c r="S201" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T201" s="1" t="n">
         <v>124</v>
@@ -20786,7 +20786,7 @@
         </is>
       </c>
       <c r="Y201" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z201" s="1" t="n">
         <v>68</v>
@@ -20815,7 +20815,7 @@
         <v>9</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="F202" s="1" t="n">
         <v>97</v>
@@ -20842,7 +20842,7 @@
         <v>10</v>
       </c>
       <c r="L202" s="1" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="M202" s="1" t="n">
         <v>75</v>
@@ -20866,10 +20866,10 @@
         </is>
       </c>
       <c r="R202" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S202" s="1" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="T202" s="1" t="n">
         <v>69</v>
@@ -20893,7 +20893,7 @@
         </is>
       </c>
       <c r="Y202" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z202" s="1" t="n">
         <v>67</v>
@@ -20922,7 +20922,7 @@
         <v>5</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F203" s="1" t="n">
         <v>114</v>
@@ -20949,7 +20949,7 @@
         <v>6</v>
       </c>
       <c r="L203" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M203" s="1" t="n">
         <v>83</v>
@@ -20973,10 +20973,10 @@
         </is>
       </c>
       <c r="R203" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="S203" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T203" s="1" t="n">
         <v>130</v>
@@ -21000,7 +21000,7 @@
         </is>
       </c>
       <c r="Y203" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z203" s="1" t="n">
         <v>71</v>
@@ -21029,7 +21029,7 @@
         <v>3</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="F204" s="1" t="n">
         <v>108</v>
@@ -21056,7 +21056,7 @@
         <v>3</v>
       </c>
       <c r="L204" s="1" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="M204" s="1" t="n">
         <v>72</v>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="R204" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S204" s="1" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="T204" s="1" t="n">
         <v>101</v>
@@ -21107,7 +21107,7 @@
         </is>
       </c>
       <c r="Y204" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z204" s="1" t="n">
         <v>70</v>
@@ -21136,7 +21136,7 @@
         <v>5</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F205" s="1" t="n">
         <v>76</v>
@@ -21163,7 +21163,7 @@
         <v>3</v>
       </c>
       <c r="L205" s="1" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="M205" s="1" t="n">
         <v>52</v>
@@ -21190,7 +21190,7 @@
         <v>5</v>
       </c>
       <c r="S205" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T205" s="1" t="n">
         <v>83</v>
@@ -21214,7 +21214,7 @@
         </is>
       </c>
       <c r="Y205" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z205" s="1" t="n">
         <v>49</v>
@@ -21243,7 +21243,7 @@
         <v>7</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="F206" s="1" t="n">
         <v>68</v>
@@ -21270,7 +21270,7 @@
         <v>5</v>
       </c>
       <c r="L206" s="1" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="M206" s="1" t="n">
         <v>49</v>
@@ -21294,7 +21294,7 @@
         </is>
       </c>
       <c r="R206" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S206" s="1" t="n">
         <v>-5</v>
@@ -21321,7 +21321,7 @@
         </is>
       </c>
       <c r="Y206" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Z206" s="1" t="n">
         <v>54</v>
@@ -21350,7 +21350,7 @@
         <v>7</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="F207" s="1" t="n">
         <v>101</v>
@@ -21377,7 +21377,7 @@
         <v>4</v>
       </c>
       <c r="L207" s="1" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="M207" s="1" t="n">
         <v>75</v>
@@ -21404,7 +21404,7 @@
         <v>10</v>
       </c>
       <c r="S207" s="1" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="T207" s="1" t="n">
         <v>110</v>
@@ -21428,7 +21428,7 @@
         </is>
       </c>
       <c r="Y207" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z207" s="1" t="n">
         <v>75</v>
@@ -21564,7 +21564,7 @@
         <v>4</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="F209" s="1" t="n">
         <v>137</v>
@@ -21591,7 +21591,7 @@
         <v>6</v>
       </c>
       <c r="L209" s="1" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="M209" s="1" t="n">
         <v>102</v>
@@ -21615,10 +21615,10 @@
         </is>
       </c>
       <c r="R209" s="1" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="S209" s="1" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T209" s="1" t="n">
         <v>155</v>
@@ -21642,7 +21642,7 @@
         </is>
       </c>
       <c r="Y209" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z209" s="1" t="n">
         <v>93</v>
@@ -21671,7 +21671,7 @@
         <v>55</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>-29</v>
+        <v>6</v>
       </c>
       <c r="F210" s="1" t="n">
         <v>957</v>
@@ -21698,7 +21698,7 @@
         <v>47</v>
       </c>
       <c r="L210" s="1" t="n">
-        <v>-37</v>
+        <v>-2</v>
       </c>
       <c r="M210" s="1" t="n">
         <v>851</v>
@@ -21722,10 +21722,10 @@
         </is>
       </c>
       <c r="R210" s="1" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="S210" s="1" t="n">
-        <v>-55</v>
+        <v>-27</v>
       </c>
       <c r="T210" s="1" t="n">
         <v>820</v>
@@ -21749,7 +21749,7 @@
         </is>
       </c>
       <c r="Y210" s="1" t="n">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="Z210" s="1" t="n">
         <v>822</v>
@@ -21778,7 +21778,7 @@
         <v>76</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>-26</v>
+        <v>-4</v>
       </c>
       <c r="F211" s="1" t="n">
         <v>756</v>
@@ -21805,7 +21805,7 @@
         <v>67</v>
       </c>
       <c r="L211" s="1" t="n">
-        <v>-35</v>
+        <v>-13</v>
       </c>
       <c r="M211" s="1" t="n">
         <v>715</v>
@@ -21829,10 +21829,10 @@
         </is>
       </c>
       <c r="R211" s="1" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="S211" s="1" t="n">
-        <v>-55</v>
+        <v>-32</v>
       </c>
       <c r="T211" s="1" t="n">
         <v>683</v>
@@ -21856,7 +21856,7 @@
         </is>
       </c>
       <c r="Y211" s="1" t="n">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="Z211" s="1" t="n">
         <v>594</v>
@@ -21885,7 +21885,7 @@
         <v>109</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="F212" s="1" t="n">
         <v>734</v>
@@ -21912,7 +21912,7 @@
         <v>66</v>
       </c>
       <c r="L212" s="1" t="n">
-        <v>-2</v>
+        <v>16</v>
       </c>
       <c r="M212" s="1" t="n">
         <v>636</v>
@@ -21936,10 +21936,10 @@
         </is>
       </c>
       <c r="R212" s="1" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="S212" s="1" t="n">
-        <v>-21</v>
+        <v>-12</v>
       </c>
       <c r="T212" s="1" t="n">
         <v>595</v>
@@ -21963,7 +21963,7 @@
         </is>
       </c>
       <c r="Y212" s="1" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="Z212" s="1" t="n">
         <v>564</v>
@@ -21992,7 +21992,7 @@
         <v>207</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>-12</v>
+        <v>33</v>
       </c>
       <c r="F213" s="1" t="n">
         <v>944</v>
@@ -22019,7 +22019,7 @@
         <v>196</v>
       </c>
       <c r="L213" s="1" t="n">
-        <v>-23</v>
+        <v>22</v>
       </c>
       <c r="M213" s="1" t="n">
         <v>874</v>
@@ -22043,10 +22043,10 @@
         </is>
       </c>
       <c r="R213" s="1" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="S213" s="1" t="n">
-        <v>-61</v>
+        <v>-15</v>
       </c>
       <c r="T213" s="1" t="n">
         <v>822</v>
@@ -22070,7 +22070,7 @@
         </is>
       </c>
       <c r="Y213" s="1" t="n">
-        <v>219</v>
+        <v>174</v>
       </c>
       <c r="Z213" s="1" t="n">
         <v>781</v>
@@ -22099,7 +22099,7 @@
         <v>73</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>-39</v>
+        <v>-4</v>
       </c>
       <c r="F214" s="1" t="n">
         <v>720</v>
@@ -22126,7 +22126,7 @@
         <v>72</v>
       </c>
       <c r="L214" s="1" t="n">
-        <v>-40</v>
+        <v>-5</v>
       </c>
       <c r="M214" s="1" t="n">
         <v>582</v>
@@ -22150,10 +22150,10 @@
         </is>
       </c>
       <c r="R214" s="1" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="S214" s="1" t="n">
-        <v>-70</v>
+        <v>-37</v>
       </c>
       <c r="T214" s="1" t="n">
         <v>554</v>
@@ -22177,7 +22177,7 @@
         </is>
       </c>
       <c r="Y214" s="1" t="n">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="Z214" s="1" t="n">
         <v>554</v>
@@ -22206,7 +22206,7 @@
         <v>139</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>-11</v>
+        <v>28</v>
       </c>
       <c r="F215" s="1" t="n">
         <v>745</v>
@@ -22233,7 +22233,7 @@
         <v>130</v>
       </c>
       <c r="L215" s="1" t="n">
-        <v>-20</v>
+        <v>19</v>
       </c>
       <c r="M215" s="1" t="n">
         <v>663</v>
@@ -22257,10 +22257,10 @@
         </is>
       </c>
       <c r="R215" s="1" t="n">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="S215" s="1" t="n">
-        <v>-26</v>
+        <v>1</v>
       </c>
       <c r="T215" s="1" t="n">
         <v>654</v>
@@ -22284,7 +22284,7 @@
         </is>
       </c>
       <c r="Y215" s="1" t="n">
-        <v>150</v>
+        <v>111</v>
       </c>
       <c r="Z215" s="1" t="n">
         <v>625</v>
@@ -22313,7 +22313,7 @@
         <v>89</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>-9</v>
+        <v>23</v>
       </c>
       <c r="F216" s="1" t="n">
         <v>803</v>
@@ -22340,7 +22340,7 @@
         <v>84</v>
       </c>
       <c r="L216" s="1" t="n">
-        <v>-14</v>
+        <v>18</v>
       </c>
       <c r="M216" s="1" t="n">
         <v>741</v>
@@ -22364,10 +22364,10 @@
         </is>
       </c>
       <c r="R216" s="1" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="S216" s="1" t="n">
-        <v>-32</v>
+        <v>-4</v>
       </c>
       <c r="T216" s="1" t="n">
         <v>779</v>
@@ -22391,7 +22391,7 @@
         </is>
       </c>
       <c r="Y216" s="1" t="n">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="Z216" s="1" t="n">
         <v>668</v>
@@ -22420,7 +22420,7 @@
         <v>60</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="F217" s="1" t="n">
         <v>710</v>
@@ -22447,7 +22447,7 @@
         <v>69</v>
       </c>
       <c r="L217" s="1" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="M217" s="1" t="n">
         <v>638</v>
@@ -22471,10 +22471,10 @@
         </is>
       </c>
       <c r="R217" s="1" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="S217" s="1" t="n">
-        <v>-31</v>
+        <v>-23</v>
       </c>
       <c r="T217" s="1" t="n">
         <v>586</v>
@@ -22498,7 +22498,7 @@
         </is>
       </c>
       <c r="Y217" s="1" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="Z217" s="1" t="n">
         <v>603</v>
@@ -22527,7 +22527,7 @@
         <v>141</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="F218" s="1" t="n">
         <v>1138</v>
@@ -22554,7 +22554,7 @@
         <v>133</v>
       </c>
       <c r="L218" s="1" t="n">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="M218" s="1" t="n">
         <v>1129</v>
@@ -22581,7 +22581,7 @@
         <v>62</v>
       </c>
       <c r="S218" s="1" t="n">
-        <v>-50</v>
+        <v>-1</v>
       </c>
       <c r="T218" s="1" t="n">
         <v>960</v>
@@ -22605,7 +22605,7 @@
         </is>
       </c>
       <c r="Y218" s="1" t="n">
-        <v>112</v>
+        <v>63</v>
       </c>
       <c r="Z218" s="1" t="n">
         <v>989</v>
@@ -22634,7 +22634,7 @@
         <v>70</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>-43</v>
+        <v>-3</v>
       </c>
       <c r="F219" s="1" t="n">
         <v>839</v>
@@ -22661,7 +22661,7 @@
         <v>79</v>
       </c>
       <c r="L219" s="1" t="n">
-        <v>-34</v>
+        <v>6</v>
       </c>
       <c r="M219" s="1" t="n">
         <v>829</v>
@@ -22685,10 +22685,10 @@
         </is>
       </c>
       <c r="R219" s="1" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="S219" s="1" t="n">
-        <v>-62</v>
+        <v>-31</v>
       </c>
       <c r="T219" s="1" t="n">
         <v>789</v>
@@ -22712,7 +22712,7 @@
         </is>
       </c>
       <c r="Y219" s="1" t="n">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="Z219" s="1" t="n">
         <v>625</v>
@@ -22741,7 +22741,7 @@
         <v>106</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>-73</v>
+        <v>42</v>
       </c>
       <c r="F220" s="1" t="n">
         <v>941</v>
@@ -22768,7 +22768,7 @@
         <v>108</v>
       </c>
       <c r="L220" s="1" t="n">
-        <v>-71</v>
+        <v>44</v>
       </c>
       <c r="M220" s="1" t="n">
         <v>944</v>
@@ -22792,10 +22792,10 @@
         </is>
       </c>
       <c r="R220" s="1" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="S220" s="1" t="n">
-        <v>-120</v>
+        <v>1</v>
       </c>
       <c r="T220" s="1" t="n">
         <v>892</v>
@@ -22819,7 +22819,7 @@
         </is>
       </c>
       <c r="Y220" s="1" t="n">
-        <v>179</v>
+        <v>64</v>
       </c>
       <c r="Z220" s="1" t="n">
         <v>803</v>
@@ -22848,7 +22848,7 @@
         <v>91</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>-14</v>
+        <v>16</v>
       </c>
       <c r="F221" s="1" t="n">
         <v>952</v>
@@ -22875,7 +22875,7 @@
         <v>95</v>
       </c>
       <c r="L221" s="1" t="n">
-        <v>-10</v>
+        <v>20</v>
       </c>
       <c r="M221" s="1" t="n">
         <v>946</v>
@@ -22899,10 +22899,10 @@
         </is>
       </c>
       <c r="R221" s="1" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="S221" s="1" t="n">
-        <v>-38</v>
+        <v>-13</v>
       </c>
       <c r="T221" s="1" t="n">
         <v>906</v>
@@ -22926,7 +22926,7 @@
         </is>
       </c>
       <c r="Y221" s="1" t="n">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="Z221" s="1" t="n">
         <v>923</v>
@@ -22955,7 +22955,7 @@
         <v>313</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>155</v>
+        <v>183</v>
       </c>
       <c r="F222" s="1" t="n">
         <v>1052</v>
@@ -22982,7 +22982,7 @@
         <v>353</v>
       </c>
       <c r="L222" s="1" t="n">
-        <v>195</v>
+        <v>223</v>
       </c>
       <c r="M222" s="1" t="n">
         <v>1090</v>
@@ -23006,10 +23006,10 @@
         </is>
       </c>
       <c r="R222" s="1" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="S222" s="1" t="n">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="T222" s="1" t="n">
         <v>909</v>
@@ -23033,7 +23033,7 @@
         </is>
       </c>
       <c r="Y222" s="1" t="n">
-        <v>158</v>
+        <v>130</v>
       </c>
       <c r="Z222" s="1" t="n">
         <v>803</v>
@@ -23062,7 +23062,7 @@
         <v>224</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="F223" s="1" t="n">
         <v>1243</v>
@@ -23089,7 +23089,7 @@
         <v>227</v>
       </c>
       <c r="L223" s="1" t="n">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="M223" s="1" t="n">
         <v>1255</v>
@@ -23113,10 +23113,10 @@
         </is>
       </c>
       <c r="R223" s="1" t="n">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="S223" s="1" t="n">
-        <v>-50</v>
+        <v>-11</v>
       </c>
       <c r="T223" s="1" t="n">
         <v>945</v>
@@ -23140,7 +23140,7 @@
         </is>
       </c>
       <c r="Y223" s="1" t="n">
-        <v>167</v>
+        <v>136</v>
       </c>
       <c r="Z223" s="1" t="n">
         <v>1075</v>
@@ -23169,7 +23169,7 @@
         <v>140</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>-161</v>
+        <v>93</v>
       </c>
       <c r="F224" s="1" t="n">
         <v>1142</v>
@@ -23196,7 +23196,7 @@
         <v>145</v>
       </c>
       <c r="L224" s="1" t="n">
-        <v>-156</v>
+        <v>98</v>
       </c>
       <c r="M224" s="1" t="n">
         <v>1142</v>
@@ -23220,10 +23220,10 @@
         </is>
       </c>
       <c r="R224" s="1" t="n">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="S224" s="1" t="n">
-        <v>-210</v>
+        <v>15</v>
       </c>
       <c r="T224" s="1" t="n">
         <v>931</v>
@@ -23247,7 +23247,7 @@
         </is>
       </c>
       <c r="Y224" s="1" t="n">
-        <v>301</v>
+        <v>47</v>
       </c>
       <c r="Z224" s="1" t="n">
         <v>903</v>
@@ -23276,7 +23276,7 @@
         <v>217</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>-32</v>
+        <v>56</v>
       </c>
       <c r="F225" s="1" t="n">
         <v>1190</v>
@@ -23303,7 +23303,7 @@
         <v>214</v>
       </c>
       <c r="L225" s="1" t="n">
-        <v>-35</v>
+        <v>53</v>
       </c>
       <c r="M225" s="1" t="n">
         <v>1190</v>
@@ -23327,10 +23327,10 @@
         </is>
       </c>
       <c r="R225" s="1" t="n">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="S225" s="1" t="n">
-        <v>-110</v>
+        <v>-34</v>
       </c>
       <c r="T225" s="1" t="n">
         <v>942</v>
@@ -23354,7 +23354,7 @@
         </is>
       </c>
       <c r="Y225" s="1" t="n">
-        <v>249</v>
+        <v>161</v>
       </c>
       <c r="Z225" s="1" t="n">
         <v>1085</v>
@@ -23383,7 +23383,7 @@
         <v>117</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>-28</v>
+        <v>75</v>
       </c>
       <c r="F226" s="1" t="n">
         <v>2262</v>
@@ -23410,7 +23410,7 @@
         <v>111</v>
       </c>
       <c r="L226" s="1" t="n">
-        <v>-34</v>
+        <v>69</v>
       </c>
       <c r="M226" s="1" t="n">
         <v>2030</v>
@@ -23434,10 +23434,10 @@
         </is>
       </c>
       <c r="R226" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="S226" s="1" t="n">
-        <v>-132</v>
+        <v>-33</v>
       </c>
       <c r="T226" s="1" t="n">
         <v>989</v>
@@ -23461,7 +23461,7 @@
         </is>
       </c>
       <c r="Y226" s="1" t="n">
-        <v>145</v>
+        <v>42</v>
       </c>
       <c r="Z226" s="1" t="n">
         <v>1984</v>
@@ -23490,7 +23490,7 @@
         <v>144</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>-39</v>
+        <v>84</v>
       </c>
       <c r="F227" s="1" t="n">
         <v>2394</v>
@@ -23517,7 +23517,7 @@
         <v>131</v>
       </c>
       <c r="L227" s="1" t="n">
-        <v>-52</v>
+        <v>71</v>
       </c>
       <c r="M227" s="1" t="n">
         <v>2175</v>
@@ -23541,10 +23541,10 @@
         </is>
       </c>
       <c r="R227" s="1" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="S227" s="1" t="n">
-        <v>-154</v>
+        <v>-47</v>
       </c>
       <c r="T227" s="1" t="n">
         <v>990</v>
@@ -23568,7 +23568,7 @@
         </is>
       </c>
       <c r="Y227" s="1" t="n">
-        <v>183</v>
+        <v>60</v>
       </c>
       <c r="Z227" s="1" t="n">
         <v>2126</v>
@@ -23597,7 +23597,7 @@
         <v>406</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>23</v>
+        <v>198</v>
       </c>
       <c r="F228" s="1" t="n">
         <v>2527</v>
@@ -23624,7 +23624,7 @@
         <v>374</v>
       </c>
       <c r="L228" s="1" t="n">
-        <v>-9</v>
+        <v>166</v>
       </c>
       <c r="M228" s="1" t="n">
         <v>2291</v>
@@ -23648,10 +23648,10 @@
         </is>
       </c>
       <c r="R228" s="1" t="n">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="S228" s="1" t="n">
-        <v>-264</v>
+        <v>-110</v>
       </c>
       <c r="T228" s="1" t="n">
         <v>972</v>
@@ -23675,7 +23675,7 @@
         </is>
       </c>
       <c r="Y228" s="1" t="n">
-        <v>383</v>
+        <v>208</v>
       </c>
       <c r="Z228" s="1" t="n">
         <v>2121</v>
@@ -23704,7 +23704,7 @@
         <v>130</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>-79</v>
+        <v>86</v>
       </c>
       <c r="F229" s="1" t="n">
         <v>2522</v>
@@ -23731,7 +23731,7 @@
         <v>142</v>
       </c>
       <c r="L229" s="1" t="n">
-        <v>-67</v>
+        <v>98</v>
       </c>
       <c r="M229" s="1" t="n">
         <v>2288</v>
@@ -23755,10 +23755,10 @@
         </is>
       </c>
       <c r="R229" s="1" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="S229" s="1" t="n">
-        <v>-174</v>
+        <v>-18</v>
       </c>
       <c r="T229" s="1" t="n">
         <v>992</v>
@@ -23782,7 +23782,7 @@
         </is>
       </c>
       <c r="Y229" s="1" t="n">
-        <v>209</v>
+        <v>44</v>
       </c>
       <c r="Z229" s="1" t="n">
         <v>2189</v>
@@ -23811,7 +23811,7 @@
         <v>45</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>-37</v>
+        <v>24</v>
       </c>
       <c r="F230" s="1" t="n">
         <v>967</v>
@@ -23838,7 +23838,7 @@
         <v>39</v>
       </c>
       <c r="L230" s="1" t="n">
-        <v>-43</v>
+        <v>18</v>
       </c>
       <c r="M230" s="1" t="n">
         <v>975</v>
@@ -23862,10 +23862,10 @@
         </is>
       </c>
       <c r="R230" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="S230" s="1" t="n">
-        <v>-69</v>
+        <v>-9</v>
       </c>
       <c r="T230" s="1" t="n">
         <v>953</v>
@@ -23889,7 +23889,7 @@
         </is>
       </c>
       <c r="Y230" s="1" t="n">
-        <v>82</v>
+        <v>21</v>
       </c>
       <c r="Z230" s="1" t="n">
         <v>841</v>
@@ -23918,7 +23918,7 @@
         <v>34</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>-50</v>
+        <v>1</v>
       </c>
       <c r="F231" s="1" t="n">
         <v>1107</v>
@@ -23945,7 +23945,7 @@
         <v>43</v>
       </c>
       <c r="L231" s="1" t="n">
-        <v>-41</v>
+        <v>10</v>
       </c>
       <c r="M231" s="1" t="n">
         <v>1110</v>
@@ -23969,10 +23969,10 @@
         </is>
       </c>
       <c r="R231" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="S231" s="1" t="n">
-        <v>-70</v>
+        <v>-22</v>
       </c>
       <c r="T231" s="1" t="n">
         <v>993</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="Y231" s="1" t="n">
-        <v>84</v>
+        <v>33</v>
       </c>
       <c r="Z231" s="1" t="n">
         <v>972</v>
@@ -24025,7 +24025,7 @@
         <v>35</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>-59</v>
+        <v>-7</v>
       </c>
       <c r="F232" s="1" t="n">
         <v>1105</v>
@@ -24052,7 +24052,7 @@
         <v>29</v>
       </c>
       <c r="L232" s="1" t="n">
-        <v>-65</v>
+        <v>-13</v>
       </c>
       <c r="M232" s="1" t="n">
         <v>1116</v>
@@ -24076,10 +24076,10 @@
         </is>
       </c>
       <c r="R232" s="1" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="S232" s="1" t="n">
-        <v>-73</v>
+        <v>-24</v>
       </c>
       <c r="T232" s="1" t="n">
         <v>978</v>
@@ -24103,7 +24103,7 @@
         </is>
       </c>
       <c r="Y232" s="1" t="n">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="Z232" s="1" t="n">
         <v>468</v>
@@ -24132,7 +24132,7 @@
         <v>29</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>-56</v>
+        <v>-25</v>
       </c>
       <c r="F233" s="1" t="n">
         <v>901</v>
@@ -24159,7 +24159,7 @@
         <v>26</v>
       </c>
       <c r="L233" s="1" t="n">
-        <v>-59</v>
+        <v>-28</v>
       </c>
       <c r="M233" s="1" t="n">
         <v>924</v>
@@ -24183,10 +24183,10 @@
         </is>
       </c>
       <c r="R233" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="S233" s="1" t="n">
-        <v>-69</v>
+        <v>-41</v>
       </c>
       <c r="T233" s="1" t="n">
         <v>915</v>
@@ -24210,7 +24210,7 @@
         </is>
       </c>
       <c r="Y233" s="1" t="n">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="Z233" s="1" t="n">
         <v>679</v>
@@ -24239,7 +24239,7 @@
         <v>118</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>-41</v>
+        <v>8</v>
       </c>
       <c r="F234" s="1" t="n">
         <v>1143</v>
@@ -24266,7 +24266,7 @@
         <v>125</v>
       </c>
       <c r="L234" s="1" t="n">
-        <v>-34</v>
+        <v>15</v>
       </c>
       <c r="M234" s="1" t="n">
         <v>1150</v>
@@ -24290,10 +24290,10 @@
         </is>
       </c>
       <c r="R234" s="1" t="n">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="S234" s="1" t="n">
-        <v>-69</v>
+        <v>-27</v>
       </c>
       <c r="T234" s="1" t="n">
         <v>987</v>
@@ -24317,7 +24317,7 @@
         </is>
       </c>
       <c r="Y234" s="1" t="n">
-        <v>159</v>
+        <v>110</v>
       </c>
       <c r="Z234" s="1" t="n">
         <v>683</v>
@@ -24346,7 +24346,7 @@
         <v>41</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>-89</v>
+        <v>-14</v>
       </c>
       <c r="F235" s="1" t="n">
         <v>1047</v>
@@ -24373,7 +24373,7 @@
         <v>40</v>
       </c>
       <c r="L235" s="1" t="n">
-        <v>-90</v>
+        <v>-15</v>
       </c>
       <c r="M235" s="1" t="n">
         <v>1060</v>
@@ -24397,10 +24397,10 @@
         </is>
       </c>
       <c r="R235" s="1" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="S235" s="1" t="n">
-        <v>-111</v>
+        <v>-41</v>
       </c>
       <c r="T235" s="1" t="n">
         <v>983</v>
@@ -24424,7 +24424,7 @@
         </is>
       </c>
       <c r="Y235" s="1" t="n">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="Z235" s="1" t="n">
         <v>731</v>
@@ -24453,7 +24453,7 @@
         <v>50</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>-35</v>
+        <v>6</v>
       </c>
       <c r="F236" s="1" t="n">
         <v>1095</v>
@@ -24480,7 +24480,7 @@
         <v>48</v>
       </c>
       <c r="L236" s="1" t="n">
-        <v>-37</v>
+        <v>4</v>
       </c>
       <c r="M236" s="1" t="n">
         <v>1108</v>
@@ -24504,10 +24504,10 @@
         </is>
       </c>
       <c r="R236" s="1" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="S236" s="1" t="n">
-        <v>-56</v>
+        <v>-21</v>
       </c>
       <c r="T236" s="1" t="n">
         <v>971</v>
@@ -24531,7 +24531,7 @@
         </is>
       </c>
       <c r="Y236" s="1" t="n">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="Z236" s="1" t="n">
         <v>625</v>
@@ -24560,7 +24560,7 @@
         <v>99</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>-45</v>
+        <v>34</v>
       </c>
       <c r="F237" s="1" t="n">
         <v>780</v>
@@ -24587,7 +24587,7 @@
         <v>93</v>
       </c>
       <c r="L237" s="1" t="n">
-        <v>-51</v>
+        <v>28</v>
       </c>
       <c r="M237" s="1" t="n">
         <v>754</v>
@@ -24611,10 +24611,10 @@
         </is>
       </c>
       <c r="R237" s="1" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="S237" s="1" t="n">
-        <v>-83</v>
+        <v>-7</v>
       </c>
       <c r="T237" s="1" t="n">
         <v>729</v>
@@ -24638,7 +24638,7 @@
         </is>
       </c>
       <c r="Y237" s="1" t="n">
-        <v>144</v>
+        <v>65</v>
       </c>
       <c r="Z237" s="1" t="n">
         <v>611</v>
@@ -24667,7 +24667,7 @@
         <v>201</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>48</v>
+        <v>119</v>
       </c>
       <c r="F238" s="1" t="n">
         <v>1141</v>
@@ -24694,7 +24694,7 @@
         <v>176</v>
       </c>
       <c r="L238" s="1" t="n">
-        <v>23</v>
+        <v>94</v>
       </c>
       <c r="M238" s="1" t="n">
         <v>1062</v>
@@ -24718,10 +24718,10 @@
         </is>
       </c>
       <c r="R238" s="1" t="n">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="S238" s="1" t="n">
-        <v>-37</v>
+        <v>25</v>
       </c>
       <c r="T238" s="1" t="n">
         <v>1089</v>
@@ -24745,7 +24745,7 @@
         </is>
       </c>
       <c r="Y238" s="1" t="n">
-        <v>153</v>
+        <v>82</v>
       </c>
       <c r="Z238" s="1" t="n">
         <v>814</v>
@@ -24774,7 +24774,7 @@
         <v>241</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="F239" s="1" t="n">
         <v>1112</v>
@@ -24801,7 +24801,7 @@
         <v>228</v>
       </c>
       <c r="L239" s="1" t="n">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="M239" s="1" t="n">
         <v>1063</v>
@@ -24825,10 +24825,10 @@
         </is>
       </c>
       <c r="R239" s="1" t="n">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="S239" s="1" t="n">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="T239" s="1" t="n">
         <v>1720</v>
@@ -24852,7 +24852,7 @@
         </is>
       </c>
       <c r="Y239" s="1" t="n">
-        <v>207</v>
+        <v>168</v>
       </c>
       <c r="Z239" s="1" t="n">
         <v>729</v>
@@ -24881,7 +24881,7 @@
         <v>643</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>235</v>
+        <v>278</v>
       </c>
       <c r="F240" s="1" t="n">
         <v>1640</v>
@@ -24908,7 +24908,7 @@
         <v>611</v>
       </c>
       <c r="L240" s="1" t="n">
-        <v>203</v>
+        <v>246</v>
       </c>
       <c r="M240" s="1" t="n">
         <v>1537</v>
@@ -24932,10 +24932,10 @@
         </is>
       </c>
       <c r="R240" s="1" t="n">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="S240" s="1" t="n">
-        <v>-176</v>
+        <v>-141</v>
       </c>
       <c r="T240" s="1" t="n">
         <v>846</v>
@@ -24959,7 +24959,7 @@
         </is>
       </c>
       <c r="Y240" s="1" t="n">
-        <v>408</v>
+        <v>365</v>
       </c>
       <c r="Z240" s="1" t="n">
         <v>1059</v>
@@ -24988,7 +24988,7 @@
         <v>249</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="F241" s="1" t="n">
         <v>1351</v>
@@ -25015,7 +25015,7 @@
         <v>251</v>
       </c>
       <c r="L241" s="1" t="n">
-        <v>83</v>
+        <v>129</v>
       </c>
       <c r="M241" s="1" t="n">
         <v>1318</v>
@@ -25042,7 +25042,7 @@
         <v>175</v>
       </c>
       <c r="S241" s="1" t="n">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="T241" s="1" t="n">
         <v>1775</v>
@@ -25066,7 +25066,7 @@
         </is>
       </c>
       <c r="Y241" s="1" t="n">
-        <v>168</v>
+        <v>122</v>
       </c>
       <c r="Z241" s="1" t="n">
         <v>924</v>
